--- a/data/corpus_liste/bnr_corpus.xlsx
+++ b/data/corpus_liste/bnr_corpus.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="350" uniqueCount="278">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="346" uniqueCount="274">
   <si>
     <t>corpus_code</t>
   </si>
@@ -36,9 +36,6 @@
     <t>archives cote</t>
   </si>
   <si>
-    <t>uuid</t>
-  </si>
-  <si>
     <t>AMR_1AEFi</t>
   </si>
   <si>
@@ -510,9 +507,6 @@
     <t>MED_AVI</t>
   </si>
   <si>
-    <t>Médiathèque – Vidéos</t>
-  </si>
-  <si>
     <t>MED_CHA</t>
   </si>
   <si>
@@ -567,12 +561,6 @@
     <t>Médiathèque - Journaux</t>
   </si>
   <si>
-    <t>MED_LAI</t>
-  </si>
-  <si>
-    <t>Médiathèque - ??</t>
-  </si>
-  <si>
     <t>MED_LET</t>
   </si>
   <si>
@@ -612,9 +600,6 @@
     <t>MED_PBI</t>
   </si>
   <si>
-    <t>Médiathèque – Collections de particuliers (suite)</t>
-  </si>
-  <si>
     <t>MED_PER</t>
   </si>
   <si>
@@ -624,9 +609,6 @@
     <t>MED_PHD</t>
   </si>
   <si>
-    <t xml:space="preserve">Médiathèque - </t>
-  </si>
-  <si>
     <t>MED_PHO</t>
   </si>
   <si>
@@ -687,93 +669,45 @@
     <t>PAR_BOH</t>
   </si>
   <si>
-    <t>Particuliers – Bohée</t>
-  </si>
-  <si>
     <t>PAR_BOU</t>
   </si>
   <si>
-    <t>Particuliers – Boussac</t>
-  </si>
-  <si>
     <t>PAR_CAT</t>
   </si>
   <si>
-    <t>Particuliers – Catrice</t>
-  </si>
-  <si>
     <t>PAR_CHI</t>
   </si>
   <si>
-    <t>Particuliers – Chirez</t>
-  </si>
-  <si>
     <t>PAR_DED</t>
   </si>
   <si>
-    <t>Particuliers – Dedaele</t>
-  </si>
-  <si>
-    <t>PAR_LAI</t>
-  </si>
-  <si>
-    <t>Particuliers - ??</t>
-  </si>
-  <si>
     <t>PAR_LAT</t>
   </si>
   <si>
-    <t>Particuliers – Latu</t>
-  </si>
-  <si>
     <t>PAR_MOR</t>
   </si>
   <si>
-    <t>Particuliers – Une Roubaisienne</t>
-  </si>
-  <si>
     <t>PAR_NAJ</t>
   </si>
   <si>
-    <t>Particuliers – Najberg</t>
-  </si>
-  <si>
     <t>PAR_NIE</t>
   </si>
   <si>
-    <t>Particuliers – Nielsen</t>
-  </si>
-  <si>
     <t>PAR_PRE</t>
   </si>
   <si>
-    <t>Particuliers – Prevost</t>
-  </si>
-  <si>
     <t>PAR_RAI</t>
   </si>
   <si>
-    <t>Particuliers – Destombes</t>
-  </si>
-  <si>
     <t>PAR_TER</t>
   </si>
   <si>
-    <t>Particuliers – Termeulen</t>
-  </si>
-  <si>
     <t>PAR_TRI</t>
   </si>
   <si>
-    <t>Particuliers – Triail</t>
-  </si>
-  <si>
     <t>PAR_TUR</t>
   </si>
   <si>
-    <t>Particuliers – Turgot</t>
-  </si>
-  <si>
     <t>PRA_AVE</t>
   </si>
   <si>
@@ -853,6 +787,60 @@
   </si>
   <si>
     <t>Archives - Commerce et industrie</t>
+  </si>
+  <si>
+    <t>Médiathèque - Collections de photographies</t>
+  </si>
+  <si>
+    <t>Médiathèque - Vidéos</t>
+  </si>
+  <si>
+    <t>Médiathèque - Collections de particuliers (suite)</t>
+  </si>
+  <si>
+    <t>Particuliers - Bohée</t>
+  </si>
+  <si>
+    <t>Particuliers - Boussac</t>
+  </si>
+  <si>
+    <t>Particuliers - Catrice</t>
+  </si>
+  <si>
+    <t>Particuliers - Chirez</t>
+  </si>
+  <si>
+    <t>Particuliers - Dedaele</t>
+  </si>
+  <si>
+    <t>Particuliers - Turgot</t>
+  </si>
+  <si>
+    <t>Particuliers - Latu</t>
+  </si>
+  <si>
+    <t>Particuliers - Une Roubaisienne</t>
+  </si>
+  <si>
+    <t>Particuliers - Najberg</t>
+  </si>
+  <si>
+    <t>Particuliers - Nielsen</t>
+  </si>
+  <si>
+    <t>Particuliers - Prevost</t>
+  </si>
+  <si>
+    <t>Particuliers - Destombes</t>
+  </si>
+  <si>
+    <t>Particuliers - Termeulen</t>
+  </si>
+  <si>
+    <t>Particuliers - Triail</t>
+  </si>
+  <si>
+    <t>fichiers</t>
   </si>
 </sst>
 </file>
@@ -1215,12 +1203,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F109"/>
+  <dimension ref="A1:F107"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16.28515625" customWidth="1"/>
-    <col min="2" max="2" width="35.5703125" customWidth="1"/>
+    <col min="2" max="2" width="71.5703125" customWidth="1"/>
     <col min="3" max="3" width="48" customWidth="1"/>
+    <col min="4" max="4" width="19.140625" customWidth="1"/>
+    <col min="5" max="5" width="16.140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1240,24 +1230,24 @@
         <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>5</v>
+        <v>273</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" t="s">
         <v>6</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
         <v>7</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>8</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>9</v>
-      </c>
-      <c r="E2" t="s">
-        <v>10</v>
       </c>
       <c r="F2">
         <v>60</v>
@@ -1265,19 +1255,19 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" t="s">
         <v>11</v>
       </c>
-      <c r="B3" t="s">
+      <c r="C3" t="s">
         <v>12</v>
       </c>
-      <c r="C3" t="s">
+      <c r="D3" t="s">
         <v>13</v>
       </c>
-      <c r="D3" t="s">
+      <c r="E3" t="s">
         <v>14</v>
-      </c>
-      <c r="E3" t="s">
-        <v>15</v>
       </c>
       <c r="F3">
         <v>97</v>
@@ -1285,19 +1275,19 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" t="s">
         <v>16</v>
       </c>
-      <c r="B4" t="s">
+      <c r="C4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D4" t="s">
         <v>17</v>
       </c>
-      <c r="C4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D4" t="s">
+      <c r="E4" t="s">
         <v>18</v>
-      </c>
-      <c r="E4" t="s">
-        <v>19</v>
       </c>
       <c r="F4">
         <v>12</v>
@@ -1305,19 +1295,19 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" t="s">
         <v>20</v>
       </c>
-      <c r="B5" t="s">
+      <c r="C5" t="s">
         <v>21</v>
       </c>
-      <c r="C5" t="s">
+      <c r="D5" t="s">
         <v>22</v>
       </c>
-      <c r="D5" t="s">
+      <c r="E5" t="s">
         <v>23</v>
-      </c>
-      <c r="E5" t="s">
-        <v>24</v>
       </c>
       <c r="F5">
         <v>23</v>
@@ -1325,16 +1315,16 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B6" t="s">
-        <v>277</v>
+        <v>255</v>
       </c>
       <c r="D6" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E6" t="s">
-        <v>271</v>
+        <v>249</v>
       </c>
       <c r="F6">
         <v>1</v>
@@ -1342,19 +1332,19 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
+        <v>25</v>
+      </c>
+      <c r="B7" t="s">
         <v>26</v>
       </c>
-      <c r="B7" t="s">
+      <c r="C7" t="s">
+        <v>12</v>
+      </c>
+      <c r="D7" t="s">
+        <v>13</v>
+      </c>
+      <c r="E7" t="s">
         <v>27</v>
-      </c>
-      <c r="C7" t="s">
-        <v>13</v>
-      </c>
-      <c r="D7" t="s">
-        <v>14</v>
-      </c>
-      <c r="E7" t="s">
-        <v>28</v>
       </c>
       <c r="F7">
         <v>15703</v>
@@ -1362,19 +1352,19 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B8" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C8" t="s">
+        <v>31</v>
+      </c>
+      <c r="D8" t="s">
         <v>32</v>
       </c>
-      <c r="D8" t="s">
-        <v>33</v>
-      </c>
       <c r="E8" t="s">
-        <v>272</v>
+        <v>250</v>
       </c>
       <c r="F8">
         <v>7</v>
@@ -1382,19 +1372,19 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
+        <v>29</v>
+      </c>
+      <c r="B9" t="s">
         <v>30</v>
       </c>
-      <c r="B9" t="s">
+      <c r="C9" t="s">
         <v>31</v>
       </c>
-      <c r="C9" t="s">
+      <c r="D9" t="s">
         <v>32</v>
       </c>
-      <c r="D9" t="s">
+      <c r="E9" t="s">
         <v>33</v>
-      </c>
-      <c r="E9" t="s">
-        <v>34</v>
       </c>
       <c r="F9">
         <v>11</v>
@@ -1402,19 +1392,19 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
+        <v>34</v>
+      </c>
+      <c r="B10" t="s">
         <v>35</v>
       </c>
-      <c r="B10" t="s">
+      <c r="C10" t="s">
+        <v>12</v>
+      </c>
+      <c r="D10" t="s">
         <v>36</v>
       </c>
-      <c r="C10" t="s">
-        <v>13</v>
-      </c>
-      <c r="D10" t="s">
+      <c r="E10" t="s">
         <v>37</v>
-      </c>
-      <c r="E10" t="s">
-        <v>38</v>
       </c>
       <c r="F10">
         <v>296</v>
@@ -1422,19 +1412,19 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
+        <v>38</v>
+      </c>
+      <c r="B11" t="s">
+        <v>113</v>
+      </c>
+      <c r="C11" t="s">
+        <v>12</v>
+      </c>
+      <c r="D11" t="s">
         <v>39</v>
       </c>
-      <c r="B11" t="s">
-        <v>114</v>
-      </c>
-      <c r="C11" t="s">
-        <v>13</v>
-      </c>
-      <c r="D11" t="s">
+      <c r="E11" t="s">
         <v>40</v>
-      </c>
-      <c r="E11" t="s">
-        <v>41</v>
       </c>
       <c r="F11">
         <v>27</v>
@@ -1442,19 +1432,19 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
+        <v>41</v>
+      </c>
+      <c r="B12" t="s">
         <v>42</v>
       </c>
-      <c r="B12" t="s">
+      <c r="C12" t="s">
+        <v>12</v>
+      </c>
+      <c r="D12" t="s">
         <v>43</v>
       </c>
-      <c r="C12" t="s">
-        <v>13</v>
-      </c>
-      <c r="D12" t="s">
+      <c r="E12" t="s">
         <v>44</v>
-      </c>
-      <c r="E12" t="s">
-        <v>45</v>
       </c>
       <c r="F12">
         <v>14</v>
@@ -1462,19 +1452,19 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
+        <v>45</v>
+      </c>
+      <c r="B13" t="s">
         <v>46</v>
       </c>
-      <c r="B13" t="s">
+      <c r="C13" t="s">
+        <v>12</v>
+      </c>
+      <c r="D13" t="s">
         <v>47</v>
       </c>
-      <c r="C13" t="s">
-        <v>13</v>
-      </c>
-      <c r="D13" t="s">
+      <c r="E13" t="s">
         <v>48</v>
-      </c>
-      <c r="E13" t="s">
-        <v>49</v>
       </c>
       <c r="F13">
         <v>5</v>
@@ -1482,19 +1472,19 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
+        <v>49</v>
+      </c>
+      <c r="B14" t="s">
         <v>50</v>
       </c>
-      <c r="B14" t="s">
+      <c r="C14" t="s">
+        <v>12</v>
+      </c>
+      <c r="D14" t="s">
         <v>51</v>
       </c>
-      <c r="C14" t="s">
-        <v>13</v>
-      </c>
-      <c r="D14" t="s">
+      <c r="E14" t="s">
         <v>52</v>
-      </c>
-      <c r="E14" t="s">
-        <v>53</v>
       </c>
       <c r="F14">
         <v>1</v>
@@ -1502,19 +1492,19 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
+        <v>53</v>
+      </c>
+      <c r="B15" t="s">
         <v>54</v>
       </c>
-      <c r="B15" t="s">
+      <c r="C15" t="s">
+        <v>31</v>
+      </c>
+      <c r="D15" t="s">
+        <v>32</v>
+      </c>
+      <c r="E15" t="s">
         <v>55</v>
-      </c>
-      <c r="C15" t="s">
-        <v>32</v>
-      </c>
-      <c r="D15" t="s">
-        <v>33</v>
-      </c>
-      <c r="E15" t="s">
-        <v>56</v>
       </c>
       <c r="F15">
         <v>496</v>
@@ -1522,16 +1512,16 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B16" t="s">
-        <v>274</v>
+        <v>252</v>
       </c>
       <c r="D16" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E16" t="s">
-        <v>275</v>
+        <v>253</v>
       </c>
       <c r="F16">
         <v>2</v>
@@ -1539,19 +1529,19 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
+        <v>57</v>
+      </c>
+      <c r="B17" t="s">
         <v>58</v>
       </c>
-      <c r="B17" t="s">
+      <c r="C17" t="s">
+        <v>12</v>
+      </c>
+      <c r="D17" t="s">
+        <v>51</v>
+      </c>
+      <c r="E17" t="s">
         <v>59</v>
-      </c>
-      <c r="C17" t="s">
-        <v>13</v>
-      </c>
-      <c r="D17" t="s">
-        <v>52</v>
-      </c>
-      <c r="E17" t="s">
-        <v>60</v>
       </c>
       <c r="F17">
         <v>3</v>
@@ -1559,19 +1549,19 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
+        <v>60</v>
+      </c>
+      <c r="B18" t="s">
         <v>61</v>
       </c>
-      <c r="B18" t="s">
+      <c r="C18" t="s">
+        <v>12</v>
+      </c>
+      <c r="D18" t="s">
+        <v>47</v>
+      </c>
+      <c r="E18" t="s">
         <v>62</v>
-      </c>
-      <c r="C18" t="s">
-        <v>13</v>
-      </c>
-      <c r="D18" t="s">
-        <v>48</v>
-      </c>
-      <c r="E18" t="s">
-        <v>63</v>
       </c>
       <c r="F18">
         <v>76590</v>
@@ -1579,19 +1569,19 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B19" t="s">
-        <v>276</v>
+        <v>254</v>
       </c>
       <c r="C19" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D19" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E19" t="s">
-        <v>273</v>
+        <v>251</v>
       </c>
       <c r="F19">
         <v>10</v>
@@ -1599,19 +1589,19 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
+        <v>64</v>
+      </c>
+      <c r="B20" t="s">
         <v>65</v>
       </c>
-      <c r="B20" t="s">
+      <c r="C20" t="s">
+        <v>21</v>
+      </c>
+      <c r="D20" t="s">
         <v>66</v>
       </c>
-      <c r="C20" t="s">
-        <v>22</v>
-      </c>
-      <c r="D20" t="s">
+      <c r="E20" t="s">
         <v>67</v>
-      </c>
-      <c r="E20" t="s">
-        <v>68</v>
       </c>
       <c r="F20">
         <v>10</v>
@@ -1619,19 +1609,19 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
+        <v>68</v>
+      </c>
+      <c r="B21" t="s">
         <v>69</v>
       </c>
-      <c r="B21" t="s">
+      <c r="C21" t="s">
         <v>70</v>
       </c>
-      <c r="C21" t="s">
+      <c r="D21" t="s">
         <v>71</v>
       </c>
-      <c r="D21" t="s">
+      <c r="E21" t="s">
         <v>72</v>
-      </c>
-      <c r="E21" t="s">
-        <v>73</v>
       </c>
       <c r="F21">
         <v>145</v>
@@ -1639,19 +1629,19 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
+        <v>73</v>
+      </c>
+      <c r="B22" t="s">
         <v>74</v>
       </c>
-      <c r="B22" t="s">
-        <v>75</v>
-      </c>
       <c r="C22" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D22" t="s">
+        <v>47</v>
+      </c>
+      <c r="E22" t="s">
         <v>48</v>
-      </c>
-      <c r="E22" t="s">
-        <v>49</v>
       </c>
       <c r="F22">
         <v>3650</v>
@@ -1659,19 +1649,19 @@
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
+        <v>75</v>
+      </c>
+      <c r="B23" t="s">
         <v>76</v>
       </c>
-      <c r="B23" t="s">
+      <c r="C23" t="s">
+        <v>12</v>
+      </c>
+      <c r="D23" t="s">
+        <v>39</v>
+      </c>
+      <c r="E23" t="s">
         <v>77</v>
-      </c>
-      <c r="C23" t="s">
-        <v>13</v>
-      </c>
-      <c r="D23" t="s">
-        <v>40</v>
-      </c>
-      <c r="E23" t="s">
-        <v>78</v>
       </c>
       <c r="F23">
         <v>604</v>
@@ -1679,13 +1669,13 @@
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
+        <v>78</v>
+      </c>
+      <c r="B24" t="s">
         <v>79</v>
       </c>
-      <c r="B24" t="s">
+      <c r="E24" t="s">
         <v>80</v>
-      </c>
-      <c r="E24" t="s">
-        <v>81</v>
       </c>
       <c r="F24">
         <v>159</v>
@@ -1693,16 +1683,16 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
+        <v>81</v>
+      </c>
+      <c r="B25" t="s">
         <v>82</v>
       </c>
-      <c r="B25" t="s">
+      <c r="D25" t="s">
         <v>83</v>
       </c>
-      <c r="D25" t="s">
+      <c r="E25" t="s">
         <v>84</v>
-      </c>
-      <c r="E25" t="s">
-        <v>85</v>
       </c>
       <c r="F25">
         <v>92</v>
@@ -1710,19 +1700,19 @@
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
+        <v>85</v>
+      </c>
+      <c r="B26" t="s">
         <v>86</v>
       </c>
-      <c r="B26" t="s">
+      <c r="C26" t="s">
+        <v>12</v>
+      </c>
+      <c r="D26" t="s">
         <v>87</v>
       </c>
-      <c r="C26" t="s">
-        <v>13</v>
-      </c>
-      <c r="D26" t="s">
+      <c r="E26" t="s">
         <v>88</v>
-      </c>
-      <c r="E26" t="s">
-        <v>89</v>
       </c>
       <c r="F26">
         <v>515</v>
@@ -1730,19 +1720,19 @@
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
+        <v>89</v>
+      </c>
+      <c r="B27" t="s">
         <v>90</v>
       </c>
-      <c r="B27" t="s">
+      <c r="C27" t="s">
+        <v>12</v>
+      </c>
+      <c r="D27" t="s">
         <v>91</v>
       </c>
-      <c r="C27" t="s">
-        <v>13</v>
-      </c>
-      <c r="D27" t="s">
-        <v>92</v>
-      </c>
       <c r="E27" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="F27">
         <v>18982</v>
@@ -1750,19 +1740,19 @@
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
+        <v>92</v>
+      </c>
+      <c r="B28" t="s">
         <v>93</v>
       </c>
-      <c r="B28" t="s">
-        <v>94</v>
-      </c>
       <c r="C28" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D28" t="s">
+        <v>47</v>
+      </c>
+      <c r="E28" t="s">
         <v>48</v>
-      </c>
-      <c r="E28" t="s">
-        <v>49</v>
       </c>
       <c r="F28">
         <v>358</v>
@@ -1770,19 +1760,19 @@
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
+        <v>94</v>
+      </c>
+      <c r="B29" t="s">
         <v>95</v>
       </c>
-      <c r="B29" t="s">
+      <c r="C29" t="s">
+        <v>12</v>
+      </c>
+      <c r="D29" t="s">
+        <v>36</v>
+      </c>
+      <c r="E29" t="s">
         <v>96</v>
-      </c>
-      <c r="C29" t="s">
-        <v>13</v>
-      </c>
-      <c r="D29" t="s">
-        <v>37</v>
-      </c>
-      <c r="E29" t="s">
-        <v>97</v>
       </c>
       <c r="F29">
         <v>170586</v>
@@ -1790,19 +1780,19 @@
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
+        <v>97</v>
+      </c>
+      <c r="B30" t="s">
         <v>98</v>
       </c>
-      <c r="B30" t="s">
+      <c r="C30" t="s">
+        <v>7</v>
+      </c>
+      <c r="D30" t="s">
         <v>99</v>
       </c>
-      <c r="C30" t="s">
-        <v>8</v>
-      </c>
-      <c r="D30" t="s">
+      <c r="E30" t="s">
         <v>100</v>
-      </c>
-      <c r="E30" t="s">
-        <v>101</v>
       </c>
       <c r="F30">
         <v>1761</v>
@@ -1810,19 +1800,19 @@
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
+        <v>101</v>
+      </c>
+      <c r="B31" t="s">
         <v>102</v>
       </c>
-      <c r="B31" t="s">
+      <c r="C31" t="s">
+        <v>12</v>
+      </c>
+      <c r="D31" t="s">
         <v>103</v>
       </c>
-      <c r="C31" t="s">
-        <v>13</v>
-      </c>
-      <c r="D31" t="s">
-        <v>104</v>
-      </c>
       <c r="E31" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F31">
         <v>358109</v>
@@ -1830,16 +1820,16 @@
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
+        <v>104</v>
+      </c>
+      <c r="B32" t="s">
         <v>105</v>
       </c>
-      <c r="B32" t="s">
-        <v>106</v>
-      </c>
       <c r="D32" t="s">
+        <v>83</v>
+      </c>
+      <c r="E32" t="s">
         <v>84</v>
-      </c>
-      <c r="E32" t="s">
-        <v>85</v>
       </c>
       <c r="F32">
         <v>32</v>
@@ -1847,19 +1837,19 @@
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
+        <v>106</v>
+      </c>
+      <c r="B33" t="s">
         <v>107</v>
       </c>
-      <c r="B33" t="s">
+      <c r="C33" t="s">
+        <v>12</v>
+      </c>
+      <c r="D33" t="s">
+        <v>47</v>
+      </c>
+      <c r="E33" t="s">
         <v>108</v>
-      </c>
-      <c r="C33" t="s">
-        <v>13</v>
-      </c>
-      <c r="D33" t="s">
-        <v>48</v>
-      </c>
-      <c r="E33" t="s">
-        <v>109</v>
       </c>
       <c r="F33">
         <v>678</v>
@@ -1867,19 +1857,19 @@
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
+        <v>109</v>
+      </c>
+      <c r="B34" t="s">
         <v>110</v>
       </c>
-      <c r="B34" t="s">
+      <c r="C34" t="s">
+        <v>70</v>
+      </c>
+      <c r="D34" t="s">
+        <v>71</v>
+      </c>
+      <c r="E34" t="s">
         <v>111</v>
-      </c>
-      <c r="C34" t="s">
-        <v>71</v>
-      </c>
-      <c r="D34" t="s">
-        <v>72</v>
-      </c>
-      <c r="E34" t="s">
-        <v>112</v>
       </c>
       <c r="F34">
         <v>174</v>
@@ -1887,19 +1877,19 @@
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
+        <v>112</v>
+      </c>
+      <c r="B35" t="s">
         <v>113</v>
       </c>
-      <c r="B35" t="s">
-        <v>114</v>
-      </c>
       <c r="C35" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D35" t="s">
+        <v>39</v>
+      </c>
+      <c r="E35" t="s">
         <v>40</v>
-      </c>
-      <c r="E35" t="s">
-        <v>41</v>
       </c>
       <c r="F35">
         <v>31</v>
@@ -1907,19 +1897,19 @@
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
+        <v>114</v>
+      </c>
+      <c r="B36" t="s">
         <v>115</v>
       </c>
-      <c r="B36" t="s">
+      <c r="C36" t="s">
         <v>116</v>
       </c>
-      <c r="C36" t="s">
+      <c r="D36" t="s">
         <v>117</v>
       </c>
-      <c r="D36" t="s">
+      <c r="E36" t="s">
         <v>118</v>
-      </c>
-      <c r="E36" t="s">
-        <v>119</v>
       </c>
       <c r="F36">
         <v>208</v>
@@ -1927,19 +1917,19 @@
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
+        <v>119</v>
+      </c>
+      <c r="B37" t="s">
         <v>120</v>
       </c>
-      <c r="B37" t="s">
+      <c r="C37" t="s">
+        <v>70</v>
+      </c>
+      <c r="D37" t="s">
+        <v>71</v>
+      </c>
+      <c r="E37" t="s">
         <v>121</v>
-      </c>
-      <c r="C37" t="s">
-        <v>71</v>
-      </c>
-      <c r="D37" t="s">
-        <v>72</v>
-      </c>
-      <c r="E37" t="s">
-        <v>122</v>
       </c>
       <c r="F37">
         <v>8812</v>
@@ -1947,16 +1937,16 @@
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
+        <v>122</v>
+      </c>
+      <c r="B38" t="s">
         <v>123</v>
       </c>
-      <c r="B38" t="s">
-        <v>124</v>
-      </c>
       <c r="D38" t="s">
+        <v>83</v>
+      </c>
+      <c r="E38" t="s">
         <v>84</v>
-      </c>
-      <c r="E38" t="s">
-        <v>85</v>
       </c>
       <c r="F38">
         <v>68</v>
@@ -1964,16 +1954,16 @@
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
+        <v>124</v>
+      </c>
+      <c r="B39" t="s">
         <v>125</v>
       </c>
-      <c r="B39" t="s">
-        <v>126</v>
-      </c>
       <c r="D39" t="s">
+        <v>83</v>
+      </c>
+      <c r="E39" t="s">
         <v>84</v>
-      </c>
-      <c r="E39" t="s">
-        <v>85</v>
       </c>
       <c r="F39">
         <v>18595</v>
@@ -1981,16 +1971,16 @@
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
+        <v>126</v>
+      </c>
+      <c r="B40" t="s">
         <v>127</v>
       </c>
-      <c r="B40" t="s">
-        <v>128</v>
-      </c>
       <c r="D40" t="s">
+        <v>83</v>
+      </c>
+      <c r="E40" t="s">
         <v>84</v>
-      </c>
-      <c r="E40" t="s">
-        <v>85</v>
       </c>
       <c r="F40">
         <v>376</v>
@@ -1998,19 +1988,19 @@
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
+        <v>128</v>
+      </c>
+      <c r="B41" t="s">
         <v>129</v>
       </c>
-      <c r="B41" t="s">
+      <c r="C41" t="s">
+        <v>12</v>
+      </c>
+      <c r="D41" t="s">
         <v>130</v>
       </c>
-      <c r="C41" t="s">
-        <v>13</v>
-      </c>
-      <c r="D41" t="s">
+      <c r="E41" t="s">
         <v>131</v>
-      </c>
-      <c r="E41" t="s">
-        <v>132</v>
       </c>
       <c r="F41">
         <v>122308</v>
@@ -2018,16 +2008,16 @@
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
+        <v>132</v>
+      </c>
+      <c r="B42" t="s">
         <v>133</v>
       </c>
-      <c r="B42" t="s">
-        <v>134</v>
-      </c>
       <c r="D42" t="s">
+        <v>83</v>
+      </c>
+      <c r="E42" t="s">
         <v>84</v>
-      </c>
-      <c r="E42" t="s">
-        <v>85</v>
       </c>
       <c r="F42">
         <v>4326</v>
@@ -2035,19 +2025,19 @@
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
+        <v>134</v>
+      </c>
+      <c r="B43" t="s">
         <v>135</v>
       </c>
-      <c r="B43" t="s">
+      <c r="C43" t="s">
+        <v>21</v>
+      </c>
+      <c r="D43" t="s">
+        <v>22</v>
+      </c>
+      <c r="E43" t="s">
         <v>136</v>
-      </c>
-      <c r="C43" t="s">
-        <v>22</v>
-      </c>
-      <c r="D43" t="s">
-        <v>23</v>
-      </c>
-      <c r="E43" t="s">
-        <v>137</v>
       </c>
       <c r="F43">
         <v>19188</v>
@@ -2055,19 +2045,19 @@
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
+        <v>137</v>
+      </c>
+      <c r="B44" t="s">
         <v>138</v>
       </c>
-      <c r="B44" t="s">
+      <c r="C44" t="s">
+        <v>7</v>
+      </c>
+      <c r="D44" t="s">
+        <v>99</v>
+      </c>
+      <c r="E44" t="s">
         <v>139</v>
-      </c>
-      <c r="C44" t="s">
-        <v>8</v>
-      </c>
-      <c r="D44" t="s">
-        <v>100</v>
-      </c>
-      <c r="E44" t="s">
-        <v>140</v>
       </c>
       <c r="F44">
         <v>4</v>
@@ -2075,19 +2065,19 @@
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
+        <v>140</v>
+      </c>
+      <c r="B45" t="s">
         <v>141</v>
       </c>
-      <c r="B45" t="s">
+      <c r="C45" t="s">
+        <v>31</v>
+      </c>
+      <c r="D45" t="s">
+        <v>32</v>
+      </c>
+      <c r="E45" t="s">
         <v>142</v>
-      </c>
-      <c r="C45" t="s">
-        <v>32</v>
-      </c>
-      <c r="D45" t="s">
-        <v>33</v>
-      </c>
-      <c r="E45" t="s">
-        <v>143</v>
       </c>
       <c r="F45">
         <v>19170</v>
@@ -2095,19 +2085,19 @@
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
+        <v>143</v>
+      </c>
+      <c r="B46" t="s">
         <v>144</v>
       </c>
-      <c r="B46" t="s">
-        <v>145</v>
-      </c>
       <c r="C46" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D46" t="s">
+        <v>36</v>
+      </c>
+      <c r="E46" t="s">
         <v>37</v>
-      </c>
-      <c r="E46" t="s">
-        <v>38</v>
       </c>
       <c r="F46">
         <v>37053</v>
@@ -2115,13 +2105,13 @@
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
+        <v>145</v>
+      </c>
+      <c r="B47" t="s">
         <v>146</v>
       </c>
-      <c r="B47" t="s">
-        <v>147</v>
-      </c>
       <c r="E47" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F47">
         <v>449</v>
@@ -2129,19 +2119,19 @@
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
+        <v>147</v>
+      </c>
+      <c r="B48" t="s">
         <v>148</v>
       </c>
-      <c r="B48" t="s">
-        <v>149</v>
-      </c>
       <c r="C48" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D48" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E48" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="F48">
         <v>7072</v>
@@ -2149,10 +2139,10 @@
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
+        <v>149</v>
+      </c>
+      <c r="B49" t="s">
         <v>150</v>
-      </c>
-      <c r="B49" t="s">
-        <v>151</v>
       </c>
       <c r="F49">
         <v>174</v>
@@ -2160,10 +2150,10 @@
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
+        <v>151</v>
+      </c>
+      <c r="B50" t="s">
         <v>152</v>
-      </c>
-      <c r="B50" t="s">
-        <v>153</v>
       </c>
       <c r="F50">
         <v>242</v>
@@ -2171,21 +2161,21 @@
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
+        <v>153</v>
+      </c>
+      <c r="B51" t="s">
         <v>154</v>
       </c>
-      <c r="B51" t="s">
-        <v>155</v>
-      </c>
       <c r="F51">
-        <v>1182</v>
+        <v>2422</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
+        <v>155</v>
+      </c>
+      <c r="B52" t="s">
         <v>156</v>
-      </c>
-      <c r="B52" t="s">
-        <v>157</v>
       </c>
       <c r="F52">
         <v>3811</v>
@@ -2193,10 +2183,10 @@
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
+        <v>157</v>
+      </c>
+      <c r="B53" t="s">
         <v>158</v>
-      </c>
-      <c r="B53" t="s">
-        <v>159</v>
       </c>
       <c r="F53">
         <v>18</v>
@@ -2204,10 +2194,10 @@
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
+        <v>159</v>
+      </c>
+      <c r="B54" t="s">
         <v>160</v>
-      </c>
-      <c r="B54" t="s">
-        <v>161</v>
       </c>
       <c r="F54">
         <v>11038</v>
@@ -2215,10 +2205,10 @@
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B55" t="s">
-        <v>163</v>
+        <v>257</v>
       </c>
       <c r="F55">
         <v>33</v>
@@ -2226,10 +2216,10 @@
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="B56" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="F56">
         <v>723</v>
@@ -2237,10 +2227,10 @@
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="B57" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="F57">
         <v>6010</v>
@@ -2248,10 +2238,10 @@
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="B58" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="F58">
         <v>365</v>
@@ -2259,10 +2249,10 @@
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="B59" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="F59">
         <v>846</v>
@@ -2270,10 +2260,10 @@
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="B60" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="F60">
         <v>2666</v>
@@ -2281,10 +2271,10 @@
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="B61" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="F61">
         <v>8485</v>
@@ -2292,10 +2282,10 @@
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="B62" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="F62">
         <v>41</v>
@@ -2303,10 +2293,10 @@
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="B63" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="F63">
         <v>9856</v>
@@ -2314,10 +2304,10 @@
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="B64" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="F64">
         <v>2174</v>
@@ -2325,493 +2315,471 @@
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="B65" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="F65">
-        <v>516</v>
+        <v>605</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="B66" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="F66">
-        <v>605</v>
+        <v>197</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="B67" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="F67">
-        <v>197</v>
+        <v>7553</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="B68" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="F68">
-        <v>7553</v>
+        <v>46262</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="B69" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="F69">
-        <v>46262</v>
+        <v>4</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="B70" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="F70">
-        <v>4</v>
+        <v>5769</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="B71" t="s">
-        <v>195</v>
+        <v>258</v>
       </c>
       <c r="F71">
-        <v>5769</v>
+        <v>1084</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="B72" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="F72">
-        <v>1084</v>
+        <v>1596</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="B73" t="s">
-        <v>199</v>
+        <v>256</v>
       </c>
       <c r="F73">
-        <v>1596</v>
+        <v>1949</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="B74" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="F74">
-        <v>1949</v>
+        <v>18844</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="B75" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="F75">
-        <v>18844</v>
+        <v>548</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="B76" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="F76">
-        <v>548</v>
+        <v>2419</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="B77" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="F77">
-        <v>2419</v>
+        <v>238</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="B78" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="F78">
-        <v>238</v>
+        <v>38231</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="B79" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="F79">
-        <v>38231</v>
+        <v>31</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="B80" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="F80">
-        <v>31</v>
+        <v>318</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="B81" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="F81">
-        <v>318</v>
+        <v>1918</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="B82" t="s">
-        <v>217</v>
+        <v>248</v>
       </c>
       <c r="F82">
-        <v>1918</v>
+        <v>375</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="B83" t="s">
-        <v>270</v>
+        <v>214</v>
       </c>
       <c r="F83">
-        <v>375</v>
+        <v>2802</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="B84" t="s">
-        <v>220</v>
+        <v>259</v>
       </c>
       <c r="F84">
-        <v>2802</v>
+        <v>638</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="B85" t="s">
-        <v>222</v>
+        <v>260</v>
       </c>
       <c r="F85">
-        <v>638</v>
+        <v>8790</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>223</v>
+        <v>217</v>
       </c>
       <c r="B86" t="s">
-        <v>224</v>
+        <v>261</v>
       </c>
       <c r="F86">
-        <v>8790</v>
+        <v>265</v>
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>225</v>
+        <v>218</v>
       </c>
       <c r="B87" t="s">
-        <v>226</v>
+        <v>262</v>
       </c>
       <c r="F87">
-        <v>265</v>
+        <v>89</v>
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>227</v>
+        <v>219</v>
       </c>
       <c r="B88" t="s">
-        <v>228</v>
+        <v>263</v>
       </c>
       <c r="F88">
-        <v>89</v>
+        <v>40</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>229</v>
+        <v>220</v>
       </c>
       <c r="B89" t="s">
-        <v>230</v>
+        <v>265</v>
       </c>
       <c r="F89">
-        <v>40</v>
+        <v>35</v>
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>231</v>
+        <v>221</v>
       </c>
       <c r="B90" t="s">
-        <v>232</v>
+        <v>266</v>
       </c>
       <c r="F90">
-        <v>724</v>
+        <v>96</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>233</v>
+        <v>222</v>
       </c>
       <c r="B91" t="s">
-        <v>234</v>
+        <v>267</v>
       </c>
       <c r="F91">
-        <v>35</v>
+        <v>23</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>235</v>
+        <v>223</v>
       </c>
       <c r="B92" t="s">
-        <v>236</v>
+        <v>268</v>
       </c>
       <c r="F92">
-        <v>96</v>
+        <v>148</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>237</v>
+        <v>224</v>
       </c>
       <c r="B93" t="s">
-        <v>238</v>
+        <v>269</v>
       </c>
       <c r="F93">
-        <v>23</v>
+        <v>3710</v>
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>239</v>
+        <v>225</v>
       </c>
       <c r="B94" t="s">
-        <v>240</v>
+        <v>270</v>
       </c>
       <c r="F94">
-        <v>148</v>
+        <v>524</v>
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>241</v>
+        <v>226</v>
       </c>
       <c r="B95" t="s">
-        <v>242</v>
+        <v>271</v>
       </c>
       <c r="F95">
-        <v>3710</v>
+        <v>884</v>
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>243</v>
+        <v>227</v>
       </c>
       <c r="B96" t="s">
-        <v>244</v>
+        <v>272</v>
       </c>
       <c r="F96">
-        <v>524</v>
+        <v>50</v>
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>245</v>
+        <v>228</v>
       </c>
       <c r="B97" t="s">
-        <v>246</v>
+        <v>264</v>
       </c>
       <c r="F97">
-        <v>884</v>
+        <v>1461</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>247</v>
+        <v>229</v>
       </c>
       <c r="B98" t="s">
-        <v>248</v>
+        <v>230</v>
       </c>
       <c r="F98">
-        <v>50</v>
+        <v>176340</v>
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>249</v>
+        <v>231</v>
       </c>
       <c r="B99" t="s">
-        <v>250</v>
+        <v>232</v>
       </c>
       <c r="F99">
-        <v>1461</v>
+        <v>3138</v>
       </c>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>251</v>
+        <v>233</v>
       </c>
       <c r="B100" t="s">
-        <v>252</v>
+        <v>234</v>
       </c>
       <c r="F100">
-        <v>176340</v>
+        <v>116806</v>
       </c>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>253</v>
+        <v>235</v>
       </c>
       <c r="B101" t="s">
-        <v>254</v>
+        <v>236</v>
       </c>
       <c r="F101">
-        <v>3138</v>
+        <v>5752</v>
       </c>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>255</v>
+        <v>237</v>
       </c>
       <c r="B102" t="s">
-        <v>256</v>
+        <v>238</v>
       </c>
       <c r="F102">
-        <v>116806</v>
+        <v>377078</v>
       </c>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>257</v>
+        <v>239</v>
       </c>
       <c r="B103" t="s">
-        <v>258</v>
+        <v>240</v>
       </c>
       <c r="F103">
-        <v>5752</v>
+        <v>64400</v>
       </c>
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>259</v>
+        <v>241</v>
       </c>
       <c r="B104" t="s">
-        <v>260</v>
+        <v>242</v>
       </c>
       <c r="F104">
-        <v>377078</v>
+        <v>595291</v>
       </c>
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>261</v>
+        <v>243</v>
       </c>
       <c r="B105" t="s">
-        <v>262</v>
+        <v>244</v>
       </c>
       <c r="F105">
-        <v>64400</v>
+        <v>3367</v>
       </c>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>263</v>
+        <v>245</v>
       </c>
       <c r="B106" t="s">
-        <v>264</v>
+        <v>246</v>
       </c>
       <c r="F106">
-        <v>595291</v>
+        <v>457</v>
       </c>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>265</v>
-      </c>
-      <c r="B107" t="s">
-        <v>266</v>
+        <v>247</v>
       </c>
       <c r="F107">
-        <v>3367</v>
-      </c>
-    </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A108" t="s">
-        <v>267</v>
-      </c>
-      <c r="B108" t="s">
-        <v>268</v>
-      </c>
-      <c r="F108">
-        <v>457</v>
-      </c>
-    </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A109" t="s">
-        <v>269</v>
-      </c>
-      <c r="F109">
         <v>4425</v>
       </c>
     </row>

--- a/data/corpus_liste/bnr_corpus.xlsx
+++ b/data/corpus_liste/bnr_corpus.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pichenotf\Dev\rbx-bnr-data\data\corpus_liste\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\corpus_liste\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -14,12 +14,15 @@
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$G$107</definedName>
+  </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="346" uniqueCount="274">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="399" uniqueCount="320">
   <si>
     <t>corpus_code</t>
   </si>
@@ -840,7 +843,145 @@
     <t>Particuliers - Triail</t>
   </si>
   <si>
-    <t>fichiers</t>
+    <t>ir</t>
+  </si>
+  <si>
+    <t>à créer par script</t>
+  </si>
+  <si>
+    <t>collection_bnr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RBX_AMR_AFF </t>
+  </si>
+  <si>
+    <t xml:space="preserve">RBX_AMR_CAD </t>
+  </si>
+  <si>
+    <t xml:space="preserve">RBX_AMR_DEL </t>
+  </si>
+  <si>
+    <t xml:space="preserve">RBX_AMR_GUE </t>
+  </si>
+  <si>
+    <t xml:space="preserve">RBX_AMR_LEB </t>
+  </si>
+  <si>
+    <t xml:space="preserve">RBX_AMR_OBJ </t>
+  </si>
+  <si>
+    <t xml:space="preserve">RBX_AMR_PHO </t>
+  </si>
+  <si>
+    <t xml:space="preserve">RBX_AMR_PLA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">RBX_AMR_PR </t>
+  </si>
+  <si>
+    <t xml:space="preserve">RBX_AMR_PUV </t>
+  </si>
+  <si>
+    <t xml:space="preserve">RBX_AMR_RAM </t>
+  </si>
+  <si>
+    <t xml:space="preserve">RBX_AMR_VIC </t>
+  </si>
+  <si>
+    <t xml:space="preserve">RBX_ARA_CPS </t>
+  </si>
+  <si>
+    <t xml:space="preserve">RBX_CSV_PAL </t>
+  </si>
+  <si>
+    <t xml:space="preserve">RBX_LAI </t>
+  </si>
+  <si>
+    <t xml:space="preserve">RBX_LAR_PUB </t>
+  </si>
+  <si>
+    <t xml:space="preserve">RBX_MDF_MTX </t>
+  </si>
+  <si>
+    <t xml:space="preserve">RBX_MED_AFF </t>
+  </si>
+  <si>
+    <t xml:space="preserve">RBX_MED_CHA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">RBX_MED_CP </t>
+  </si>
+  <si>
+    <t xml:space="preserve">RBX_MED_DIL </t>
+  </si>
+  <si>
+    <t xml:space="preserve">RBX_MED_EPH </t>
+  </si>
+  <si>
+    <t xml:space="preserve">RBX_MED_FLR </t>
+  </si>
+  <si>
+    <t xml:space="preserve">RBX_MED_FOO </t>
+  </si>
+  <si>
+    <t xml:space="preserve">RBX_MED_IMA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">RBX_MED_LET </t>
+  </si>
+  <si>
+    <t xml:space="preserve">RBX_MED_MAR </t>
+  </si>
+  <si>
+    <t xml:space="preserve">RBX_MED_MON </t>
+  </si>
+  <si>
+    <t xml:space="preserve">RBX_MED_MS </t>
+  </si>
+  <si>
+    <t xml:space="preserve">RBX_MED_PAR </t>
+  </si>
+  <si>
+    <t xml:space="preserve">RBX_MED_PHO </t>
+  </si>
+  <si>
+    <t xml:space="preserve">RBX_MED_PLA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">RBX_MED_PUB </t>
+  </si>
+  <si>
+    <t xml:space="preserve">RBX_MED_VDM </t>
+  </si>
+  <si>
+    <t xml:space="preserve">RBX_MUS_ARC </t>
+  </si>
+  <si>
+    <t xml:space="preserve">RBX_MUS_VAI </t>
+  </si>
+  <si>
+    <t xml:space="preserve">RBX_OBS_JOU </t>
+  </si>
+  <si>
+    <t xml:space="preserve">RBX_PRA_AVE </t>
+  </si>
+  <si>
+    <t xml:space="preserve">RBX_PRA_CRT </t>
+  </si>
+  <si>
+    <t xml:space="preserve">RBX_PRA_CTG </t>
+  </si>
+  <si>
+    <t xml:space="preserve">RBX_PRA_ERT </t>
+  </si>
+  <si>
+    <t xml:space="preserve">RBX_PRA_IND </t>
+  </si>
+  <si>
+    <t xml:space="preserve">RBX_PRA_JRX </t>
+  </si>
+  <si>
+    <t xml:space="preserve">RBX_VAH_PUB </t>
   </si>
 </sst>
 </file>
@@ -869,7 +1010,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -892,13 +1033,27 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
@@ -1203,7 +1358,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F107"/>
+  <dimension ref="A1:G107"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16.28515625" customWidth="1"/>
@@ -1211,9 +1366,11 @@
     <col min="3" max="3" width="48" customWidth="1"/>
     <col min="4" max="4" width="19.140625" customWidth="1"/>
     <col min="5" max="5" width="16.140625" customWidth="1"/>
+    <col min="6" max="6" width="17.42578125" customWidth="1"/>
+    <col min="7" max="7" width="21.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1229,11 +1386,14 @@
       <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="2" t="s">
         <v>273</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G1" s="2" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -1249,11 +1409,8 @@
       <c r="E2" t="s">
         <v>9</v>
       </c>
-      <c r="F2">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>10</v>
       </c>
@@ -1269,11 +1426,8 @@
       <c r="E3" t="s">
         <v>14</v>
       </c>
-      <c r="F3">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>15</v>
       </c>
@@ -1289,11 +1443,8 @@
       <c r="E4" t="s">
         <v>18</v>
       </c>
-      <c r="F4">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>19</v>
       </c>
@@ -1309,11 +1460,8 @@
       <c r="E5" t="s">
         <v>23</v>
       </c>
-      <c r="F5">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>24</v>
       </c>
@@ -1326,11 +1474,8 @@
       <c r="E6" t="s">
         <v>249</v>
       </c>
-      <c r="F6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>25</v>
       </c>
@@ -1346,11 +1491,8 @@
       <c r="E7" t="s">
         <v>27</v>
       </c>
-      <c r="F7">
-        <v>15703</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>28</v>
       </c>
@@ -1366,11 +1508,8 @@
       <c r="E8" t="s">
         <v>250</v>
       </c>
-      <c r="F8">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>29</v>
       </c>
@@ -1386,11 +1525,8 @@
       <c r="E9" t="s">
         <v>33</v>
       </c>
-      <c r="F9">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>34</v>
       </c>
@@ -1406,11 +1542,8 @@
       <c r="E10" t="s">
         <v>37</v>
       </c>
-      <c r="F10">
-        <v>296</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>38</v>
       </c>
@@ -1426,11 +1559,8 @@
       <c r="E11" t="s">
         <v>40</v>
       </c>
-      <c r="F11">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>41</v>
       </c>
@@ -1446,11 +1576,8 @@
       <c r="E12" t="s">
         <v>44</v>
       </c>
-      <c r="F12">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>45</v>
       </c>
@@ -1466,11 +1593,8 @@
       <c r="E13" t="s">
         <v>48</v>
       </c>
-      <c r="F13">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>49</v>
       </c>
@@ -1486,11 +1610,8 @@
       <c r="E14" t="s">
         <v>52</v>
       </c>
-      <c r="F14">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>53</v>
       </c>
@@ -1506,11 +1627,8 @@
       <c r="E15" t="s">
         <v>55</v>
       </c>
-      <c r="F15">
-        <v>496</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>56</v>
       </c>
@@ -1523,11 +1641,8 @@
       <c r="E16" t="s">
         <v>253</v>
       </c>
-      <c r="F16">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>57</v>
       </c>
@@ -1543,11 +1658,8 @@
       <c r="E17" t="s">
         <v>59</v>
       </c>
-      <c r="F17">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>60</v>
       </c>
@@ -1563,11 +1675,8 @@
       <c r="E18" t="s">
         <v>62</v>
       </c>
-      <c r="F18">
-        <v>76590</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>63</v>
       </c>
@@ -1583,11 +1692,8 @@
       <c r="E19" t="s">
         <v>251</v>
       </c>
-      <c r="F19">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>64</v>
       </c>
@@ -1603,11 +1709,8 @@
       <c r="E20" t="s">
         <v>67</v>
       </c>
-      <c r="F20">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>68</v>
       </c>
@@ -1623,11 +1726,8 @@
       <c r="E21" t="s">
         <v>72</v>
       </c>
-      <c r="F21">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>73</v>
       </c>
@@ -1643,11 +1743,11 @@
       <c r="E22" t="s">
         <v>48</v>
       </c>
-      <c r="F22">
-        <v>3650</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G22" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>75</v>
       </c>
@@ -1663,11 +1763,8 @@
       <c r="E23" t="s">
         <v>77</v>
       </c>
-      <c r="F23">
-        <v>604</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>78</v>
       </c>
@@ -1677,11 +1774,8 @@
       <c r="E24" t="s">
         <v>80</v>
       </c>
-      <c r="F24">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>81</v>
       </c>
@@ -1694,11 +1788,8 @@
       <c r="E25" t="s">
         <v>84</v>
       </c>
-      <c r="F25">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>85</v>
       </c>
@@ -1714,11 +1805,11 @@
       <c r="E26" t="s">
         <v>88</v>
       </c>
-      <c r="F26">
-        <v>515</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G26" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>89</v>
       </c>
@@ -1734,11 +1825,8 @@
       <c r="E27" t="s">
         <v>91</v>
       </c>
-      <c r="F27">
-        <v>18982</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>92</v>
       </c>
@@ -1754,11 +1842,8 @@
       <c r="E28" t="s">
         <v>48</v>
       </c>
-      <c r="F28">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>94</v>
       </c>
@@ -1774,11 +1859,11 @@
       <c r="E29" t="s">
         <v>96</v>
       </c>
-      <c r="F29">
-        <v>170586</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G29" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>97</v>
       </c>
@@ -1794,11 +1879,8 @@
       <c r="E30" t="s">
         <v>100</v>
       </c>
-      <c r="F30">
-        <v>1761</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>101</v>
       </c>
@@ -1814,11 +1896,8 @@
       <c r="E31" t="s">
         <v>103</v>
       </c>
-      <c r="F31">
-        <v>358109</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>104</v>
       </c>
@@ -1831,11 +1910,8 @@
       <c r="E32" t="s">
         <v>84</v>
       </c>
-      <c r="F32">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>106</v>
       </c>
@@ -1851,11 +1927,11 @@
       <c r="E33" t="s">
         <v>108</v>
       </c>
-      <c r="F33">
-        <v>678</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G33" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>109</v>
       </c>
@@ -1871,11 +1947,11 @@
       <c r="E34" t="s">
         <v>111</v>
       </c>
-      <c r="F34">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G34" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>112</v>
       </c>
@@ -1891,11 +1967,8 @@
       <c r="E35" t="s">
         <v>40</v>
       </c>
-      <c r="F35">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>114</v>
       </c>
@@ -1911,11 +1984,11 @@
       <c r="E36" t="s">
         <v>118</v>
       </c>
-      <c r="F36">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G36" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>119</v>
       </c>
@@ -1931,11 +2004,8 @@
       <c r="E37" t="s">
         <v>121</v>
       </c>
-      <c r="F37">
-        <v>8812</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>122</v>
       </c>
@@ -1948,11 +2018,8 @@
       <c r="E38" t="s">
         <v>84</v>
       </c>
-      <c r="F38">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>124</v>
       </c>
@@ -1965,11 +2032,11 @@
       <c r="E39" t="s">
         <v>84</v>
       </c>
-      <c r="F39">
-        <v>18595</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G39" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>126</v>
       </c>
@@ -1982,11 +2049,11 @@
       <c r="E40" t="s">
         <v>84</v>
       </c>
-      <c r="F40">
-        <v>376</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G40" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>128</v>
       </c>
@@ -2002,11 +2069,8 @@
       <c r="E41" t="s">
         <v>131</v>
       </c>
-      <c r="F41">
-        <v>122308</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>132</v>
       </c>
@@ -2019,11 +2083,11 @@
       <c r="E42" t="s">
         <v>84</v>
       </c>
-      <c r="F42">
-        <v>4326</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G42" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>134</v>
       </c>
@@ -2039,11 +2103,11 @@
       <c r="E43" t="s">
         <v>136</v>
       </c>
-      <c r="F43">
-        <v>19188</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G43" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>137</v>
       </c>
@@ -2059,11 +2123,8 @@
       <c r="E44" t="s">
         <v>139</v>
       </c>
-      <c r="F44">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>140</v>
       </c>
@@ -2079,11 +2140,8 @@
       <c r="E45" t="s">
         <v>142</v>
       </c>
-      <c r="F45">
-        <v>19170</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>143</v>
       </c>
@@ -2099,11 +2157,11 @@
       <c r="E46" t="s">
         <v>37</v>
       </c>
-      <c r="F46">
-        <v>37053</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G46" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>145</v>
       </c>
@@ -2113,11 +2171,8 @@
       <c r="E47" t="s">
         <v>80</v>
       </c>
-      <c r="F47">
-        <v>449</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>147</v>
       </c>
@@ -2133,657 +2188,601 @@
       <c r="E48" t="s">
         <v>108</v>
       </c>
-      <c r="F48">
-        <v>7072</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G48" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>149</v>
       </c>
       <c r="B49" t="s">
         <v>150</v>
       </c>
-      <c r="F49">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G49" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>151</v>
       </c>
       <c r="B50" t="s">
         <v>152</v>
       </c>
-      <c r="F50">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G50" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>153</v>
       </c>
       <c r="B51" t="s">
         <v>154</v>
       </c>
-      <c r="F51">
-        <v>2422</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G51" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>155</v>
       </c>
       <c r="B52" t="s">
         <v>156</v>
       </c>
-      <c r="F52">
-        <v>3811</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G52" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>157</v>
       </c>
       <c r="B53" t="s">
         <v>158</v>
       </c>
-      <c r="F53">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G53" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>159</v>
       </c>
       <c r="B54" t="s">
         <v>160</v>
       </c>
-      <c r="F54">
-        <v>11038</v>
-      </c>
-    </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G54" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>161</v>
       </c>
       <c r="B55" t="s">
         <v>257</v>
       </c>
-      <c r="F55">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>162</v>
       </c>
       <c r="B56" t="s">
         <v>163</v>
       </c>
-      <c r="F56">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G56" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>164</v>
       </c>
       <c r="B57" t="s">
         <v>165</v>
       </c>
-      <c r="F57">
-        <v>6010</v>
-      </c>
-    </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G57" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>166</v>
       </c>
       <c r="B58" t="s">
         <v>167</v>
       </c>
-      <c r="F58">
-        <v>365</v>
-      </c>
-    </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G58" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>168</v>
       </c>
       <c r="B59" t="s">
         <v>169</v>
       </c>
-      <c r="F59">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G59" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>170</v>
       </c>
       <c r="B60" t="s">
         <v>171</v>
       </c>
-      <c r="F60">
-        <v>2666</v>
-      </c>
-    </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="61" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>172</v>
       </c>
       <c r="B61" t="s">
         <v>173</v>
       </c>
-      <c r="F61">
-        <v>8485</v>
-      </c>
-    </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G61" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>174</v>
       </c>
       <c r="B62" t="s">
         <v>175</v>
       </c>
-      <c r="F62">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G62" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>176</v>
       </c>
       <c r="B63" t="s">
         <v>177</v>
       </c>
-      <c r="F63">
-        <v>9856</v>
-      </c>
-    </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G63" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>178</v>
       </c>
       <c r="B64" t="s">
         <v>179</v>
       </c>
-      <c r="F64">
-        <v>2174</v>
-      </c>
-    </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="65" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>180</v>
       </c>
       <c r="B65" t="s">
         <v>181</v>
       </c>
-      <c r="F65">
-        <v>605</v>
-      </c>
-    </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G65" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>182</v>
       </c>
       <c r="B66" t="s">
         <v>183</v>
       </c>
-      <c r="F66">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G66" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>184</v>
       </c>
       <c r="B67" t="s">
         <v>185</v>
       </c>
-      <c r="F67">
-        <v>7553</v>
-      </c>
-    </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G67" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>186</v>
       </c>
       <c r="B68" t="s">
         <v>187</v>
       </c>
-      <c r="F68">
-        <v>46262</v>
-      </c>
-    </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G68" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>188</v>
       </c>
       <c r="B69" t="s">
         <v>189</v>
       </c>
-      <c r="F69">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="70" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>190</v>
       </c>
       <c r="B70" t="s">
         <v>191</v>
       </c>
-      <c r="F70">
-        <v>5769</v>
-      </c>
-    </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G70" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="71" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>192</v>
       </c>
       <c r="B71" t="s">
         <v>258</v>
       </c>
-      <c r="F71">
-        <v>1084</v>
-      </c>
-    </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="72" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>193</v>
       </c>
       <c r="B72" t="s">
         <v>194</v>
       </c>
-      <c r="F72">
-        <v>1596</v>
-      </c>
-    </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="73" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>195</v>
       </c>
       <c r="B73" t="s">
         <v>256</v>
       </c>
-      <c r="F73">
-        <v>1949</v>
-      </c>
-    </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="74" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>196</v>
       </c>
       <c r="B74" t="s">
         <v>197</v>
       </c>
-      <c r="F74">
-        <v>18844</v>
-      </c>
-    </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G74" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="75" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>198</v>
       </c>
       <c r="B75" t="s">
         <v>199</v>
       </c>
-      <c r="F75">
-        <v>548</v>
-      </c>
-    </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G75" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="76" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>200</v>
       </c>
       <c r="B76" t="s">
         <v>201</v>
       </c>
-      <c r="F76">
-        <v>2419</v>
-      </c>
-    </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G76" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="77" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>202</v>
       </c>
       <c r="B77" t="s">
         <v>203</v>
       </c>
-      <c r="F77">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="78" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>204</v>
       </c>
       <c r="B78" t="s">
         <v>205</v>
       </c>
-      <c r="F78">
-        <v>38231</v>
-      </c>
-    </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G78" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="79" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>206</v>
       </c>
       <c r="B79" t="s">
         <v>207</v>
       </c>
-      <c r="F79">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="80" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>208</v>
       </c>
       <c r="B80" t="s">
         <v>209</v>
       </c>
-      <c r="F80">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G80" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="81" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>210</v>
       </c>
       <c r="B81" t="s">
         <v>211</v>
       </c>
-      <c r="F81">
-        <v>1918</v>
-      </c>
-    </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G81" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="82" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>212</v>
       </c>
       <c r="B82" t="s">
         <v>248</v>
       </c>
-      <c r="F82">
-        <v>375</v>
-      </c>
-    </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="83" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>213</v>
       </c>
       <c r="B83" t="s">
         <v>214</v>
       </c>
-      <c r="F83">
-        <v>2802</v>
-      </c>
-    </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G83" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="84" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>215</v>
       </c>
       <c r="B84" t="s">
         <v>259</v>
       </c>
-      <c r="F84">
-        <v>638</v>
-      </c>
-    </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="85" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>216</v>
       </c>
       <c r="B85" t="s">
         <v>260</v>
       </c>
-      <c r="F85">
-        <v>8790</v>
-      </c>
-    </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="86" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>217</v>
       </c>
       <c r="B86" t="s">
         <v>261</v>
       </c>
-      <c r="F86">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="87" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>218</v>
       </c>
       <c r="B87" t="s">
         <v>262</v>
       </c>
-      <c r="F87">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="88" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>219</v>
       </c>
       <c r="B88" t="s">
         <v>263</v>
       </c>
-      <c r="F88">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="89" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>220</v>
       </c>
       <c r="B89" t="s">
         <v>265</v>
       </c>
-      <c r="F89">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="90" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>221</v>
       </c>
       <c r="B90" t="s">
         <v>266</v>
       </c>
-      <c r="F90">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="91" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>222</v>
       </c>
       <c r="B91" t="s">
         <v>267</v>
       </c>
-      <c r="F91">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="92" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>223</v>
       </c>
       <c r="B92" t="s">
         <v>268</v>
       </c>
-      <c r="F92">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="93" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>224</v>
       </c>
       <c r="B93" t="s">
         <v>269</v>
       </c>
-      <c r="F93">
-        <v>3710</v>
-      </c>
-    </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="94" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>225</v>
       </c>
       <c r="B94" t="s">
         <v>270</v>
       </c>
-      <c r="F94">
-        <v>524</v>
-      </c>
-    </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="95" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>226</v>
       </c>
       <c r="B95" t="s">
         <v>271</v>
       </c>
-      <c r="F95">
-        <v>884</v>
-      </c>
-    </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="96" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>227</v>
       </c>
       <c r="B96" t="s">
         <v>272</v>
       </c>
-      <c r="F96">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="97" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>228</v>
       </c>
       <c r="B97" t="s">
         <v>264</v>
       </c>
-      <c r="F97">
-        <v>1461</v>
-      </c>
-    </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="98" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>229</v>
       </c>
       <c r="B98" t="s">
         <v>230</v>
       </c>
-      <c r="F98">
-        <v>176340</v>
-      </c>
-    </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F98" t="s">
+        <v>274</v>
+      </c>
+      <c r="G98" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="99" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>231</v>
       </c>
       <c r="B99" t="s">
         <v>232</v>
       </c>
-      <c r="F99">
-        <v>3138</v>
-      </c>
-    </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="100" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>233</v>
       </c>
       <c r="B100" t="s">
         <v>234</v>
       </c>
-      <c r="F100">
-        <v>116806</v>
-      </c>
-    </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F100" t="s">
+        <v>274</v>
+      </c>
+      <c r="G100" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="101" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>235</v>
       </c>
       <c r="B101" t="s">
         <v>236</v>
       </c>
-      <c r="F101">
-        <v>5752</v>
-      </c>
-    </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F101" t="s">
+        <v>274</v>
+      </c>
+      <c r="G101" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="102" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>237</v>
       </c>
       <c r="B102" t="s">
         <v>238</v>
       </c>
-      <c r="F102">
-        <v>377078</v>
-      </c>
-    </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F102" t="s">
+        <v>274</v>
+      </c>
+      <c r="G102" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="103" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>239</v>
       </c>
       <c r="B103" t="s">
         <v>240</v>
       </c>
-      <c r="F103">
-        <v>64400</v>
-      </c>
-    </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F103" t="s">
+        <v>274</v>
+      </c>
+      <c r="G103" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="104" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>241</v>
       </c>
       <c r="B104" t="s">
         <v>242</v>
       </c>
-      <c r="F104">
-        <v>595291</v>
-      </c>
-    </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F104" t="s">
+        <v>274</v>
+      </c>
+      <c r="G104" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="105" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>243</v>
       </c>
       <c r="B105" t="s">
         <v>244</v>
       </c>
-      <c r="F105">
-        <v>3367</v>
-      </c>
-    </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F105" t="s">
+        <v>274</v>
+      </c>
+      <c r="G105" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="106" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>245</v>
       </c>
       <c r="B106" t="s">
         <v>246</v>
       </c>
-      <c r="F106">
-        <v>457</v>
-      </c>
-    </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G106" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="107" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>247</v>
       </c>
-      <c r="F107">
-        <v>4425</v>
-      </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:G107"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/corpus_liste/bnr_corpus.xlsx
+++ b/data/corpus_liste/bnr_corpus.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\corpus_liste\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pichenotf\Dev\rbx-bnr-data\data\corpus_liste\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="399" uniqueCount="320">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="402" uniqueCount="321">
   <si>
     <t>corpus_code</t>
   </si>
@@ -982,6 +982,9 @@
   </si>
   <si>
     <t xml:space="preserve">RBX_VAH_PUB </t>
+  </si>
+  <si>
+    <t>notes</t>
   </si>
 </sst>
 </file>
@@ -1048,12 +1051,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
@@ -1358,7 +1364,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G107"/>
+  <dimension ref="A1:H107"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16.28515625" customWidth="1"/>
@@ -1367,10 +1373,10 @@
     <col min="4" max="4" width="19.140625" customWidth="1"/>
     <col min="5" max="5" width="16.140625" customWidth="1"/>
     <col min="6" max="6" width="17.42578125" customWidth="1"/>
-    <col min="7" max="7" width="21.85546875" customWidth="1"/>
+    <col min="7" max="8" width="21.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1392,8 +1398,11 @@
       <c r="G1" s="2" t="s">
         <v>275</v>
       </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H1" s="3" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -1410,7 +1419,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>10</v>
       </c>
@@ -1427,7 +1436,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>15</v>
       </c>
@@ -1444,7 +1453,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>19</v>
       </c>
@@ -1461,7 +1470,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>24</v>
       </c>
@@ -1475,7 +1484,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>25</v>
       </c>
@@ -1492,7 +1501,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>28</v>
       </c>
@@ -1509,7 +1518,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>29</v>
       </c>
@@ -1526,7 +1535,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>34</v>
       </c>
@@ -1543,7 +1552,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>38</v>
       </c>
@@ -1560,7 +1569,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>41</v>
       </c>
@@ -1577,7 +1586,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>45</v>
       </c>
@@ -1594,7 +1603,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>49</v>
       </c>
@@ -1611,7 +1620,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>53</v>
       </c>
@@ -1628,7 +1637,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>56</v>
       </c>
@@ -1859,6 +1868,9 @@
       <c r="E29" t="s">
         <v>96</v>
       </c>
+      <c r="F29" t="s">
+        <v>274</v>
+      </c>
       <c r="G29" t="s">
         <v>278</v>
       </c>
@@ -2156,6 +2168,9 @@
       </c>
       <c r="E46" t="s">
         <v>37</v>
+      </c>
+      <c r="F46" t="s">
+        <v>274</v>
       </c>
       <c r="G46" t="s">
         <v>286</v>

--- a/data/corpus_liste/bnr_corpus.xlsx
+++ b/data/corpus_liste/bnr_corpus.xlsx
@@ -15,14 +15,14 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$G$107</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$G$93</definedName>
   </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="402" uniqueCount="321">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="374" uniqueCount="293">
   <si>
     <t>corpus_code</t>
   </si>
@@ -669,48 +669,6 @@
     <t>Observatoire urbain de Roubaix  - Journaux de quartier</t>
   </si>
   <si>
-    <t>PAR_BOH</t>
-  </si>
-  <si>
-    <t>PAR_BOU</t>
-  </si>
-  <si>
-    <t>PAR_CAT</t>
-  </si>
-  <si>
-    <t>PAR_CHI</t>
-  </si>
-  <si>
-    <t>PAR_DED</t>
-  </si>
-  <si>
-    <t>PAR_LAT</t>
-  </si>
-  <si>
-    <t>PAR_MOR</t>
-  </si>
-  <si>
-    <t>PAR_NAJ</t>
-  </si>
-  <si>
-    <t>PAR_NIE</t>
-  </si>
-  <si>
-    <t>PAR_PRE</t>
-  </si>
-  <si>
-    <t>PAR_RAI</t>
-  </si>
-  <si>
-    <t>PAR_TER</t>
-  </si>
-  <si>
-    <t>PAR_TRI</t>
-  </si>
-  <si>
-    <t>PAR_TUR</t>
-  </si>
-  <si>
     <t>PRA_AVE</t>
   </si>
   <si>
@@ -799,48 +757,6 @@
   </si>
   <si>
     <t>Médiathèque - Collections de particuliers (suite)</t>
-  </si>
-  <si>
-    <t>Particuliers - Bohée</t>
-  </si>
-  <si>
-    <t>Particuliers - Boussac</t>
-  </si>
-  <si>
-    <t>Particuliers - Catrice</t>
-  </si>
-  <si>
-    <t>Particuliers - Chirez</t>
-  </si>
-  <si>
-    <t>Particuliers - Dedaele</t>
-  </si>
-  <si>
-    <t>Particuliers - Turgot</t>
-  </si>
-  <si>
-    <t>Particuliers - Latu</t>
-  </si>
-  <si>
-    <t>Particuliers - Une Roubaisienne</t>
-  </si>
-  <si>
-    <t>Particuliers - Najberg</t>
-  </si>
-  <si>
-    <t>Particuliers - Nielsen</t>
-  </si>
-  <si>
-    <t>Particuliers - Prevost</t>
-  </si>
-  <si>
-    <t>Particuliers - Destombes</t>
-  </si>
-  <si>
-    <t>Particuliers - Termeulen</t>
-  </si>
-  <si>
-    <t>Particuliers - Triail</t>
   </si>
   <si>
     <t>ir</t>
@@ -1364,7 +1280,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H107"/>
+  <dimension ref="A1:H93"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16.28515625" customWidth="1"/>
@@ -1393,13 +1309,13 @@
         <v>4</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>273</v>
+        <v>245</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>275</v>
+        <v>247</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>320</v>
+        <v>292</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
@@ -1475,13 +1391,13 @@
         <v>24</v>
       </c>
       <c r="B6" t="s">
-        <v>255</v>
+        <v>241</v>
       </c>
       <c r="D6" t="s">
         <v>130</v>
       </c>
       <c r="E6" t="s">
-        <v>249</v>
+        <v>235</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
@@ -1515,7 +1431,7 @@
         <v>32</v>
       </c>
       <c r="E8" t="s">
-        <v>250</v>
+        <v>236</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
@@ -1642,13 +1558,13 @@
         <v>56</v>
       </c>
       <c r="B16" t="s">
-        <v>252</v>
+        <v>238</v>
       </c>
       <c r="D16" t="s">
         <v>99</v>
       </c>
       <c r="E16" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
@@ -1690,7 +1606,7 @@
         <v>63</v>
       </c>
       <c r="B19" t="s">
-        <v>254</v>
+        <v>240</v>
       </c>
       <c r="C19" t="s">
         <v>12</v>
@@ -1699,7 +1615,7 @@
         <v>51</v>
       </c>
       <c r="E19" t="s">
-        <v>251</v>
+        <v>237</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
@@ -1753,7 +1669,7 @@
         <v>48</v>
       </c>
       <c r="G22" t="s">
-        <v>276</v>
+        <v>248</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
@@ -1815,7 +1731,7 @@
         <v>88</v>
       </c>
       <c r="G26" t="s">
-        <v>277</v>
+        <v>249</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
@@ -1869,10 +1785,10 @@
         <v>96</v>
       </c>
       <c r="F29" t="s">
-        <v>274</v>
+        <v>246</v>
       </c>
       <c r="G29" t="s">
-        <v>278</v>
+        <v>250</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
@@ -1940,7 +1856,7 @@
         <v>108</v>
       </c>
       <c r="G33" t="s">
-        <v>279</v>
+        <v>251</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
@@ -1960,7 +1876,7 @@
         <v>111</v>
       </c>
       <c r="G34" t="s">
-        <v>280</v>
+        <v>252</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
@@ -1997,7 +1913,7 @@
         <v>118</v>
       </c>
       <c r="G36" t="s">
-        <v>281</v>
+        <v>253</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
@@ -2045,7 +1961,7 @@
         <v>84</v>
       </c>
       <c r="G39" t="s">
-        <v>282</v>
+        <v>254</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
@@ -2062,7 +1978,7 @@
         <v>84</v>
       </c>
       <c r="G40" t="s">
-        <v>283</v>
+        <v>255</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
@@ -2096,7 +2012,7 @@
         <v>84</v>
       </c>
       <c r="G42" t="s">
-        <v>284</v>
+        <v>256</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
@@ -2116,7 +2032,7 @@
         <v>136</v>
       </c>
       <c r="G43" t="s">
-        <v>285</v>
+        <v>257</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
@@ -2170,10 +2086,10 @@
         <v>37</v>
       </c>
       <c r="F46" t="s">
-        <v>274</v>
+        <v>246</v>
       </c>
       <c r="G46" t="s">
-        <v>286</v>
+        <v>258</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
@@ -2204,7 +2120,7 @@
         <v>108</v>
       </c>
       <c r="G48" t="s">
-        <v>287</v>
+        <v>259</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
@@ -2215,7 +2131,7 @@
         <v>150</v>
       </c>
       <c r="G49" t="s">
-        <v>288</v>
+        <v>260</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
@@ -2226,7 +2142,7 @@
         <v>152</v>
       </c>
       <c r="G50" t="s">
-        <v>289</v>
+        <v>261</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
@@ -2237,7 +2153,7 @@
         <v>154</v>
       </c>
       <c r="G51" t="s">
-        <v>290</v>
+        <v>262</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
@@ -2248,7 +2164,7 @@
         <v>156</v>
       </c>
       <c r="G52" t="s">
-        <v>291</v>
+        <v>263</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
@@ -2259,7 +2175,7 @@
         <v>158</v>
       </c>
       <c r="G53" t="s">
-        <v>292</v>
+        <v>264</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.25">
@@ -2270,7 +2186,7 @@
         <v>160</v>
       </c>
       <c r="G54" t="s">
-        <v>293</v>
+        <v>265</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
@@ -2278,7 +2194,7 @@
         <v>161</v>
       </c>
       <c r="B55" t="s">
-        <v>257</v>
+        <v>243</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
@@ -2289,7 +2205,7 @@
         <v>163</v>
       </c>
       <c r="G56" t="s">
-        <v>294</v>
+        <v>266</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.25">
@@ -2300,7 +2216,7 @@
         <v>165</v>
       </c>
       <c r="G57" t="s">
-        <v>295</v>
+        <v>267</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.25">
@@ -2311,7 +2227,7 @@
         <v>167</v>
       </c>
       <c r="G58" t="s">
-        <v>296</v>
+        <v>268</v>
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.25">
@@ -2322,7 +2238,7 @@
         <v>169</v>
       </c>
       <c r="G59" t="s">
-        <v>297</v>
+        <v>269</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.25">
@@ -2341,7 +2257,7 @@
         <v>173</v>
       </c>
       <c r="G61" t="s">
-        <v>298</v>
+        <v>270</v>
       </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.25">
@@ -2352,7 +2268,7 @@
         <v>175</v>
       </c>
       <c r="G62" t="s">
-        <v>299</v>
+        <v>271</v>
       </c>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.25">
@@ -2363,7 +2279,7 @@
         <v>177</v>
       </c>
       <c r="G63" t="s">
-        <v>300</v>
+        <v>272</v>
       </c>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.25">
@@ -2382,7 +2298,7 @@
         <v>181</v>
       </c>
       <c r="G65" t="s">
-        <v>301</v>
+        <v>273</v>
       </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.25">
@@ -2393,7 +2309,7 @@
         <v>183</v>
       </c>
       <c r="G66" t="s">
-        <v>302</v>
+        <v>274</v>
       </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.25">
@@ -2404,7 +2320,7 @@
         <v>185</v>
       </c>
       <c r="G67" t="s">
-        <v>303</v>
+        <v>275</v>
       </c>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.25">
@@ -2415,7 +2331,7 @@
         <v>187</v>
       </c>
       <c r="G68" t="s">
-        <v>304</v>
+        <v>276</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.25">
@@ -2434,7 +2350,7 @@
         <v>191</v>
       </c>
       <c r="G70" t="s">
-        <v>305</v>
+        <v>277</v>
       </c>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.25">
@@ -2442,7 +2358,7 @@
         <v>192</v>
       </c>
       <c r="B71" t="s">
-        <v>258</v>
+        <v>244</v>
       </c>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.25">
@@ -2458,7 +2374,7 @@
         <v>195</v>
       </c>
       <c r="B73" t="s">
-        <v>256</v>
+        <v>242</v>
       </c>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.25">
@@ -2469,7 +2385,7 @@
         <v>197</v>
       </c>
       <c r="G74" t="s">
-        <v>306</v>
+        <v>278</v>
       </c>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.25">
@@ -2480,7 +2396,7 @@
         <v>199</v>
       </c>
       <c r="G75" t="s">
-        <v>307</v>
+        <v>279</v>
       </c>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.25">
@@ -2491,7 +2407,7 @@
         <v>201</v>
       </c>
       <c r="G76" t="s">
-        <v>308</v>
+        <v>280</v>
       </c>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.25">
@@ -2510,7 +2426,7 @@
         <v>205</v>
       </c>
       <c r="G78" t="s">
-        <v>309</v>
+        <v>281</v>
       </c>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.25">
@@ -2529,7 +2445,7 @@
         <v>209</v>
       </c>
       <c r="G80" t="s">
-        <v>310</v>
+        <v>282</v>
       </c>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.25">
@@ -2540,7 +2456,7 @@
         <v>211</v>
       </c>
       <c r="G81" t="s">
-        <v>311</v>
+        <v>283</v>
       </c>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.25">
@@ -2548,7 +2464,7 @@
         <v>212</v>
       </c>
       <c r="B82" t="s">
-        <v>248</v>
+        <v>234</v>
       </c>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.25">
@@ -2559,7 +2475,7 @@
         <v>214</v>
       </c>
       <c r="G83" t="s">
-        <v>312</v>
+        <v>284</v>
       </c>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.25">
@@ -2567,237 +2483,125 @@
         <v>215</v>
       </c>
       <c r="B84" t="s">
-        <v>259</v>
+        <v>216</v>
+      </c>
+      <c r="F84" t="s">
+        <v>246</v>
+      </c>
+      <c r="G84" t="s">
+        <v>285</v>
       </c>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B85" t="s">
-        <v>260</v>
+        <v>218</v>
       </c>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="B86" t="s">
-        <v>261</v>
+        <v>220</v>
+      </c>
+      <c r="F86" t="s">
+        <v>246</v>
+      </c>
+      <c r="G86" t="s">
+        <v>286</v>
       </c>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="B87" t="s">
-        <v>262</v>
+        <v>222</v>
+      </c>
+      <c r="F87" t="s">
+        <v>246</v>
+      </c>
+      <c r="G87" t="s">
+        <v>287</v>
       </c>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="B88" t="s">
-        <v>263</v>
+        <v>224</v>
+      </c>
+      <c r="F88" t="s">
+        <v>246</v>
+      </c>
+      <c r="G88" t="s">
+        <v>288</v>
       </c>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="B89" t="s">
-        <v>265</v>
+        <v>226</v>
+      </c>
+      <c r="F89" t="s">
+        <v>246</v>
+      </c>
+      <c r="G89" t="s">
+        <v>289</v>
       </c>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>221</v>
+        <v>227</v>
       </c>
       <c r="B90" t="s">
-        <v>266</v>
+        <v>228</v>
+      </c>
+      <c r="F90" t="s">
+        <v>246</v>
+      </c>
+      <c r="G90" t="s">
+        <v>290</v>
       </c>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="B91" t="s">
-        <v>267</v>
+        <v>230</v>
+      </c>
+      <c r="F91" t="s">
+        <v>246</v>
+      </c>
+      <c r="G91" t="s">
+        <v>291</v>
       </c>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>223</v>
+        <v>231</v>
       </c>
       <c r="B92" t="s">
-        <v>268</v>
+        <v>232</v>
+      </c>
+      <c r="G92" t="s">
+        <v>291</v>
       </c>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>224</v>
-      </c>
-      <c r="B93" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="94" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A94" t="s">
-        <v>225</v>
-      </c>
-      <c r="B94" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="95" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A95" t="s">
-        <v>226</v>
-      </c>
-      <c r="B95" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="96" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A96" t="s">
-        <v>227</v>
-      </c>
-      <c r="B96" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="97" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A97" t="s">
-        <v>228</v>
-      </c>
-      <c r="B97" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="98" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A98" t="s">
-        <v>229</v>
-      </c>
-      <c r="B98" t="s">
-        <v>230</v>
-      </c>
-      <c r="F98" t="s">
-        <v>274</v>
-      </c>
-      <c r="G98" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="99" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A99" t="s">
-        <v>231</v>
-      </c>
-      <c r="B99" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="100" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A100" t="s">
         <v>233</v>
       </c>
-      <c r="B100" t="s">
-        <v>234</v>
-      </c>
-      <c r="F100" t="s">
-        <v>274</v>
-      </c>
-      <c r="G100" t="s">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="101" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A101" t="s">
-        <v>235</v>
-      </c>
-      <c r="B101" t="s">
-        <v>236</v>
-      </c>
-      <c r="F101" t="s">
-        <v>274</v>
-      </c>
-      <c r="G101" t="s">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="102" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A102" t="s">
-        <v>237</v>
-      </c>
-      <c r="B102" t="s">
-        <v>238</v>
-      </c>
-      <c r="F102" t="s">
-        <v>274</v>
-      </c>
-      <c r="G102" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="103" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A103" t="s">
-        <v>239</v>
-      </c>
-      <c r="B103" t="s">
-        <v>240</v>
-      </c>
-      <c r="F103" t="s">
-        <v>274</v>
-      </c>
-      <c r="G103" t="s">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="104" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A104" t="s">
-        <v>241</v>
-      </c>
-      <c r="B104" t="s">
-        <v>242</v>
-      </c>
-      <c r="F104" t="s">
-        <v>274</v>
-      </c>
-      <c r="G104" t="s">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="105" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A105" t="s">
-        <v>243</v>
-      </c>
-      <c r="B105" t="s">
-        <v>244</v>
-      </c>
-      <c r="F105" t="s">
-        <v>274</v>
-      </c>
-      <c r="G105" t="s">
-        <v>319</v>
-      </c>
-    </row>
-    <row r="106" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A106" t="s">
-        <v>245</v>
-      </c>
-      <c r="B106" t="s">
-        <v>246</v>
-      </c>
-      <c r="G106" t="s">
-        <v>319</v>
-      </c>
-    </row>
-    <row r="107" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A107" t="s">
-        <v>247</v>
-      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G107"/>
+  <autoFilter ref="A1:G93"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/corpus_liste/bnr_corpus.xlsx
+++ b/data/corpus_liste/bnr_corpus.xlsx
@@ -10,6 +10,9 @@
   <sheets>
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId3"/>
   </sheets>
+  <definedNames>
+    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">Sheet1!$A$1:$I$93</definedName>
+  </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
@@ -20,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="467" uniqueCount="297">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="467" uniqueCount="298">
   <si>
     <t xml:space="preserve">corpus_code</t>
   </si>
@@ -901,13 +904,16 @@
     <t xml:space="preserve">Presse - Roubaix-Tourcoing</t>
   </si>
   <si>
+    <t xml:space="preserve">RBX_PRA_RTG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VAH_PUB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ville d'art et d'histoire  - Publications</t>
+  </si>
+  <si>
     <t xml:space="preserve">RBX_VAH_PUB </t>
-  </si>
-  <si>
-    <t xml:space="preserve">VAH_PUB</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ville d'art et d'histoire  - Publications</t>
   </si>
   <si>
     <t xml:space="preserve">_INCONNU</t>
@@ -951,12 +957,18 @@
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor rgb="FFFFFFCC"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -1000,13 +1012,21 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -1018,7 +1038,36 @@
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
+  <dxfs count="3">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF000000"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1203,1595 +1252,1600 @@
   </sheetPr>
   <dimension ref="A1:I93"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="26.8"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="9" min="2" style="1" width="8.54"/>
+  </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="2" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
+      <c r="A2" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="0" t="s">
+      <c r="B2" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C2" s="0" t="s">
+      <c r="C2" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D2" s="0" t="s">
+      <c r="D2" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="E2" s="0" t="s">
+      <c r="E2" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="I2" s="0" t="s">
+      <c r="I2" s="3" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
+      <c r="A3" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B3" s="0" t="s">
+      <c r="B3" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="C3" s="0" t="s">
+      <c r="C3" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="D3" s="0" t="s">
+      <c r="D3" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="E3" s="0" t="s">
+      <c r="E3" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="I3" s="0" t="s">
+      <c r="I3" s="3" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
+      <c r="A4" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="B4" s="0" t="s">
+      <c r="B4" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="C4" s="0" t="s">
+      <c r="C4" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D4" s="0" t="s">
+      <c r="D4" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="E4" s="0" t="s">
+      <c r="E4" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="I4" s="0" t="s">
+      <c r="I4" s="3" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
+      <c r="A5" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="B5" s="0" t="s">
+      <c r="B5" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="C5" s="0" t="s">
+      <c r="C5" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="D5" s="0" t="s">
+      <c r="D5" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="E5" s="0" t="s">
+      <c r="E5" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="I5" s="0" t="s">
+      <c r="I5" s="3" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="s">
+      <c r="A6" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="B6" s="0" t="s">
+      <c r="B6" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="D6" s="0" t="s">
+      <c r="D6" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="E6" s="0" t="s">
+      <c r="E6" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="I6" s="0" t="s">
+      <c r="I6" s="3" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="s">
+      <c r="A7" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="B7" s="0" t="s">
+      <c r="B7" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="C7" s="0" t="s">
+      <c r="C7" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="D7" s="0" t="s">
+      <c r="D7" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="E7" s="0" t="s">
+      <c r="E7" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="I7" s="0" t="s">
+      <c r="I7" s="3" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="s">
+      <c r="A8" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="B8" s="0" t="s">
+      <c r="B8" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="C8" s="0" t="s">
+      <c r="C8" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="D8" s="0" t="s">
+      <c r="D8" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="E8" s="0" t="s">
+      <c r="E8" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="I8" s="0" t="s">
+      <c r="I8" s="3" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0" t="s">
+      <c r="A9" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B9" s="0" t="s">
+      <c r="B9" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="C9" s="0" t="s">
+      <c r="C9" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="D9" s="0" t="s">
+      <c r="D9" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="E9" s="0" t="s">
+      <c r="E9" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="I9" s="0" t="s">
+      <c r="I9" s="3" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="0" t="s">
+      <c r="A10" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="B10" s="0" t="s">
+      <c r="B10" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="C10" s="0" t="s">
+      <c r="C10" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="D10" s="0" t="s">
+      <c r="D10" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="E10" s="0" t="s">
+      <c r="E10" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="I10" s="0" t="s">
+      <c r="I10" s="3" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="0" t="s">
+      <c r="A11" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="B11" s="0" t="s">
+      <c r="B11" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="C11" s="0" t="s">
+      <c r="C11" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="D11" s="0" t="s">
+      <c r="D11" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="E11" s="0" t="s">
+      <c r="E11" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="I11" s="0" t="s">
+      <c r="I11" s="3" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="0" t="s">
+      <c r="A12" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="B12" s="0" t="s">
+      <c r="B12" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="C12" s="0" t="s">
+      <c r="C12" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="D12" s="0" t="s">
+      <c r="D12" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="E12" s="0" t="s">
+      <c r="E12" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="I12" s="0" t="s">
+      <c r="I12" s="3" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="0" t="s">
+      <c r="A13" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="B13" s="0" t="s">
+      <c r="B13" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="C13" s="0" t="s">
+      <c r="C13" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="D13" s="0" t="s">
+      <c r="D13" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="E13" s="0" t="s">
+      <c r="E13" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="I13" s="0" t="s">
+      <c r="I13" s="3" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="0" t="s">
+      <c r="A14" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="B14" s="0" t="s">
+      <c r="B14" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="C14" s="0" t="s">
+      <c r="C14" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="D14" s="0" t="s">
+      <c r="D14" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="E14" s="0" t="s">
+      <c r="E14" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="I14" s="0" t="s">
+      <c r="I14" s="3" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="0" t="s">
+      <c r="A15" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="B15" s="0" t="s">
+      <c r="B15" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="C15" s="0" t="s">
+      <c r="C15" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="D15" s="0" t="s">
+      <c r="D15" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="E15" s="0" t="s">
+      <c r="E15" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="I15" s="0" t="s">
+      <c r="I15" s="3" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="0" t="s">
+      <c r="A16" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="B16" s="0" t="s">
+      <c r="B16" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="D16" s="0" t="s">
+      <c r="D16" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="E16" s="0" t="s">
+      <c r="E16" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="I16" s="0" t="s">
+      <c r="I16" s="3" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="0" t="s">
+      <c r="A17" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="B17" s="0" t="s">
+      <c r="B17" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="C17" s="0" t="s">
+      <c r="C17" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="D17" s="0" t="s">
+      <c r="D17" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="E17" s="0" t="s">
+      <c r="E17" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="I17" s="0" t="s">
+      <c r="I17" s="3" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="0" t="s">
+      <c r="A18" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="B18" s="0" t="s">
+      <c r="B18" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="C18" s="0" t="s">
+      <c r="C18" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="D18" s="0" t="s">
+      <c r="D18" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="E18" s="0" t="s">
+      <c r="E18" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="I18" s="0" t="s">
+      <c r="I18" s="3" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="0" t="s">
+      <c r="A19" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="B19" s="0" t="s">
+      <c r="B19" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="C19" s="0" t="s">
+      <c r="C19" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="D19" s="0" t="s">
+      <c r="D19" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="E19" s="0" t="s">
+      <c r="E19" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="I19" s="0" t="s">
+      <c r="I19" s="3" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="0" t="s">
+      <c r="A20" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="B20" s="0" t="s">
+      <c r="B20" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="C20" s="0" t="s">
+      <c r="C20" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="D20" s="0" t="s">
+      <c r="D20" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="E20" s="0" t="s">
+      <c r="E20" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="I20" s="0" t="s">
+      <c r="I20" s="3" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="0" t="s">
+      <c r="A21" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="B21" s="0" t="s">
+      <c r="B21" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="C21" s="0" t="s">
+      <c r="C21" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="D21" s="0" t="s">
+      <c r="D21" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="E21" s="0" t="s">
+      <c r="E21" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="I21" s="0" t="s">
+      <c r="I21" s="3" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="0" t="s">
+      <c r="A22" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="B22" s="0" t="s">
+      <c r="B22" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="C22" s="0" t="s">
+      <c r="C22" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="0" t="s">
+      <c r="D22" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="E22" s="0" t="s">
+      <c r="E22" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="G22" s="0" t="s">
+      <c r="G22" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="I22" s="0" t="s">
+      <c r="I22" s="3" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="0" t="s">
+      <c r="A23" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="B23" s="0" t="s">
+      <c r="B23" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="C23" s="0" t="s">
+      <c r="C23" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="D23" s="0" t="s">
+      <c r="D23" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="E23" s="0" t="s">
+      <c r="E23" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="I23" s="0" t="s">
+      <c r="I23" s="3" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="0" t="s">
+      <c r="A24" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="B24" s="0" t="s">
+      <c r="B24" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="E24" s="0" t="s">
+      <c r="E24" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="I24" s="0" t="s">
+      <c r="I24" s="3" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="0" t="s">
+      <c r="A25" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="B25" s="0" t="s">
+      <c r="B25" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="D25" s="0" t="s">
+      <c r="D25" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="E25" s="0" t="s">
+      <c r="E25" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="I25" s="0" t="s">
+      <c r="I25" s="3" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="0" t="s">
+      <c r="A26" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="B26" s="0" t="s">
+      <c r="B26" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="C26" s="0" t="s">
+      <c r="C26" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="D26" s="0" t="s">
+      <c r="D26" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="E26" s="0" t="s">
+      <c r="E26" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="G26" s="0" t="s">
+      <c r="G26" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="I26" s="0" t="s">
+      <c r="I26" s="3" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="0" t="s">
+      <c r="A27" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="B27" s="0" t="s">
+      <c r="B27" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="C27" s="0" t="s">
+      <c r="C27" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="D27" s="0" t="s">
+      <c r="D27" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="E27" s="0" t="s">
+      <c r="E27" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="I27" s="0" t="s">
+      <c r="I27" s="3" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="0" t="s">
+      <c r="A28" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="B28" s="0" t="s">
+      <c r="B28" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="C28" s="0" t="s">
+      <c r="C28" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="D28" s="0" t="s">
+      <c r="D28" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="E28" s="0" t="s">
+      <c r="E28" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="I28" s="0" t="s">
+      <c r="I28" s="3" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="0" t="s">
+      <c r="A29" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="B29" s="0" t="s">
+      <c r="B29" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="C29" s="0" t="s">
+      <c r="C29" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="D29" s="0" t="s">
+      <c r="D29" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="E29" s="0" t="s">
+      <c r="E29" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="F29" s="0" t="s">
+      <c r="F29" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="G29" s="0" t="s">
+      <c r="G29" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="I29" s="0" t="s">
+      <c r="I29" s="3" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="0" t="s">
+      <c r="A30" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="B30" s="0" t="s">
+      <c r="B30" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="C30" s="0" t="s">
+      <c r="C30" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D30" s="0" t="s">
+      <c r="D30" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="E30" s="0" t="s">
+      <c r="E30" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="I30" s="0" t="s">
+      <c r="I30" s="3" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="0" t="s">
+      <c r="A31" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="B31" s="0" t="s">
+      <c r="B31" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="C31" s="0" t="s">
+      <c r="C31" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="D31" s="0" t="s">
+      <c r="D31" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="E31" s="0" t="s">
+      <c r="E31" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="I31" s="0" t="s">
+      <c r="I31" s="3" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="0" t="s">
+      <c r="A32" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="B32" s="0" t="s">
+      <c r="B32" s="3" t="s">
         <v>124</v>
       </c>
-      <c r="D32" s="0" t="s">
+      <c r="D32" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="E32" s="0" t="s">
+      <c r="E32" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="I32" s="0" t="s">
+      <c r="I32" s="3" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="0" t="s">
+      <c r="A33" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="B33" s="0" t="s">
+      <c r="B33" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="C33" s="0" t="s">
+      <c r="C33" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="D33" s="0" t="s">
+      <c r="D33" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="E33" s="0" t="s">
+      <c r="E33" s="3" t="s">
         <v>127</v>
       </c>
-      <c r="G33" s="0" t="s">
+      <c r="G33" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="I33" s="0" t="s">
+      <c r="I33" s="3" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="0" t="s">
+      <c r="A34" s="3" t="s">
         <v>129</v>
       </c>
-      <c r="B34" s="0" t="s">
+      <c r="B34" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="C34" s="0" t="s">
+      <c r="C34" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="D34" s="0" t="s">
+      <c r="D34" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="E34" s="0" t="s">
+      <c r="E34" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="G34" s="0" t="s">
+      <c r="G34" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="I34" s="0" t="s">
+      <c r="I34" s="3" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="0" t="s">
+      <c r="A35" s="3" t="s">
         <v>133</v>
       </c>
-      <c r="B35" s="0" t="s">
+      <c r="B35" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="C35" s="0" t="s">
+      <c r="C35" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="D35" s="0" t="s">
+      <c r="D35" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="E35" s="0" t="s">
+      <c r="E35" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="I35" s="0" t="s">
+      <c r="I35" s="3" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="0" t="s">
+      <c r="A36" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="B36" s="0" t="s">
+      <c r="B36" s="3" t="s">
         <v>135</v>
       </c>
-      <c r="C36" s="0" t="s">
+      <c r="C36" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="D36" s="0" t="s">
+      <c r="D36" s="3" t="s">
         <v>137</v>
       </c>
-      <c r="E36" s="0" t="s">
+      <c r="E36" s="3" t="s">
         <v>138</v>
       </c>
-      <c r="G36" s="0" t="s">
+      <c r="G36" s="3" t="s">
         <v>139</v>
       </c>
-      <c r="I36" s="0" t="s">
+      <c r="I36" s="3" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="0" t="s">
+      <c r="A37" s="3" t="s">
         <v>140</v>
       </c>
-      <c r="B37" s="0" t="s">
+      <c r="B37" s="3" t="s">
         <v>141</v>
       </c>
-      <c r="C37" s="0" t="s">
+      <c r="C37" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="D37" s="0" t="s">
+      <c r="D37" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="E37" s="0" t="s">
+      <c r="E37" s="3" t="s">
         <v>142</v>
       </c>
-      <c r="I37" s="0" t="s">
+      <c r="I37" s="3" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="0" t="s">
+      <c r="A38" s="3" t="s">
         <v>143</v>
       </c>
-      <c r="B38" s="0" t="s">
+      <c r="B38" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="D38" s="0" t="s">
+      <c r="D38" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="E38" s="0" t="s">
+      <c r="E38" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="I38" s="0" t="s">
+      <c r="I38" s="3" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="0" t="s">
+      <c r="A39" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="B39" s="0" t="s">
+      <c r="B39" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="D39" s="0" t="s">
+      <c r="D39" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="E39" s="0" t="s">
+      <c r="E39" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="G39" s="0" t="s">
+      <c r="G39" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="I39" s="0" t="s">
+      <c r="I39" s="3" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="0" t="s">
+      <c r="A40" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="B40" s="0" t="s">
+      <c r="B40" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="D40" s="0" t="s">
+      <c r="D40" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="E40" s="0" t="s">
+      <c r="E40" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="G40" s="0" t="s">
+      <c r="G40" s="3" t="s">
         <v>150</v>
       </c>
-      <c r="I40" s="0" t="s">
+      <c r="I40" s="3" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="0" t="s">
+      <c r="A41" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="B41" s="0" t="s">
+      <c r="B41" s="3" t="s">
         <v>152</v>
       </c>
-      <c r="C41" s="0" t="s">
+      <c r="C41" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="D41" s="0" t="s">
+      <c r="D41" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="E41" s="0" t="s">
+      <c r="E41" s="3" t="s">
         <v>153</v>
       </c>
-      <c r="I41" s="0" t="s">
+      <c r="I41" s="3" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="0" t="s">
+      <c r="A42" s="3" t="s">
         <v>154</v>
       </c>
-      <c r="B42" s="0" t="s">
+      <c r="B42" s="3" t="s">
         <v>155</v>
       </c>
-      <c r="D42" s="0" t="s">
+      <c r="D42" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="E42" s="0" t="s">
+      <c r="E42" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="G42" s="0" t="s">
+      <c r="G42" s="3" t="s">
         <v>156</v>
       </c>
-      <c r="I42" s="0" t="s">
+      <c r="I42" s="3" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="0" t="s">
+      <c r="A43" s="3" t="s">
         <v>157</v>
       </c>
-      <c r="B43" s="0" t="s">
+      <c r="B43" s="3" t="s">
         <v>158</v>
       </c>
-      <c r="C43" s="0" t="s">
+      <c r="C43" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="D43" s="0" t="s">
+      <c r="D43" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="E43" s="0" t="s">
+      <c r="E43" s="3" t="s">
         <v>159</v>
       </c>
-      <c r="G43" s="0" t="s">
+      <c r="G43" s="3" t="s">
         <v>160</v>
       </c>
-      <c r="I43" s="0" t="s">
+      <c r="I43" s="3" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="0" t="s">
+      <c r="A44" s="3" t="s">
         <v>161</v>
       </c>
-      <c r="B44" s="0" t="s">
+      <c r="B44" s="3" t="s">
         <v>162</v>
       </c>
-      <c r="C44" s="0" t="s">
+      <c r="C44" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D44" s="0" t="s">
+      <c r="D44" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="E44" s="0" t="s">
+      <c r="E44" s="3" t="s">
         <v>163</v>
       </c>
-      <c r="I44" s="0" t="s">
+      <c r="I44" s="3" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="0" t="s">
+      <c r="A45" s="3" t="s">
         <v>164</v>
       </c>
-      <c r="B45" s="0" t="s">
+      <c r="B45" s="3" t="s">
         <v>165</v>
       </c>
-      <c r="C45" s="0" t="s">
+      <c r="C45" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="0" t="s">
+      <c r="D45" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="E45" s="0" t="s">
+      <c r="E45" s="3" t="s">
         <v>166</v>
       </c>
-      <c r="I45" s="0" t="s">
+      <c r="I45" s="3" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="0" t="s">
+      <c r="A46" s="3" t="s">
         <v>167</v>
       </c>
-      <c r="B46" s="0" t="s">
+      <c r="B46" s="3" t="s">
         <v>168</v>
       </c>
-      <c r="C46" s="0" t="s">
+      <c r="C46" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="D46" s="0" t="s">
+      <c r="D46" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="E46" s="0" t="s">
+      <c r="E46" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="F46" s="0" t="s">
+      <c r="F46" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="G46" s="0" t="s">
+      <c r="G46" s="3" t="s">
         <v>169</v>
       </c>
-      <c r="I46" s="0" t="s">
+      <c r="I46" s="3" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="0" t="s">
+      <c r="A47" s="3" t="s">
         <v>170</v>
       </c>
-      <c r="B47" s="0" t="s">
+      <c r="B47" s="3" t="s">
         <v>171</v>
       </c>
-      <c r="E47" s="0" t="s">
+      <c r="E47" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="I47" s="0" t="s">
+      <c r="I47" s="3" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="0" t="s">
+      <c r="A48" s="3" t="s">
         <v>172</v>
       </c>
-      <c r="B48" s="0" t="s">
+      <c r="B48" s="3" t="s">
         <v>173</v>
       </c>
-      <c r="C48" s="0" t="s">
+      <c r="C48" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="D48" s="0" t="s">
+      <c r="D48" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="E48" s="0" t="s">
+      <c r="E48" s="3" t="s">
         <v>174</v>
       </c>
-      <c r="G48" s="0" t="s">
+      <c r="G48" s="3" t="s">
         <v>175</v>
       </c>
-      <c r="I48" s="0" t="s">
+      <c r="I48" s="3" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="0" t="s">
+      <c r="A49" s="3" t="s">
         <v>176</v>
       </c>
-      <c r="B49" s="0" t="s">
+      <c r="B49" s="3" t="s">
         <v>177</v>
       </c>
-      <c r="G49" s="0" t="s">
+      <c r="G49" s="3" t="s">
         <v>178</v>
       </c>
-      <c r="I49" s="0" t="s">
+      <c r="I49" s="3" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="0" t="s">
+      <c r="A50" s="3" t="s">
         <v>179</v>
       </c>
-      <c r="B50" s="0" t="s">
+      <c r="B50" s="3" t="s">
         <v>180</v>
       </c>
-      <c r="G50" s="0" t="s">
+      <c r="G50" s="3" t="s">
         <v>181</v>
       </c>
-      <c r="I50" s="0" t="s">
+      <c r="I50" s="3" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="0" t="s">
+      <c r="A51" s="3" t="s">
         <v>182</v>
       </c>
-      <c r="B51" s="0" t="s">
+      <c r="B51" s="3" t="s">
         <v>183</v>
       </c>
-      <c r="G51" s="0" t="s">
+      <c r="G51" s="3" t="s">
         <v>184</v>
       </c>
-      <c r="I51" s="0" t="s">
+      <c r="I51" s="3" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="0" t="s">
+      <c r="A52" s="3" t="s">
         <v>185</v>
       </c>
-      <c r="B52" s="0" t="s">
+      <c r="B52" s="3" t="s">
         <v>186</v>
       </c>
-      <c r="G52" s="0" t="s">
+      <c r="G52" s="3" t="s">
         <v>187</v>
       </c>
-      <c r="I52" s="0" t="s">
+      <c r="I52" s="3" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="0" t="s">
+      <c r="A53" s="3" t="s">
         <v>188</v>
       </c>
-      <c r="B53" s="0" t="s">
+      <c r="B53" s="3" t="s">
         <v>189</v>
       </c>
-      <c r="G53" s="0" t="s">
+      <c r="G53" s="3" t="s">
         <v>190</v>
       </c>
-      <c r="I53" s="0" t="s">
+      <c r="I53" s="3" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="0" t="s">
+      <c r="A54" s="3" t="s">
         <v>191</v>
       </c>
-      <c r="B54" s="0" t="s">
+      <c r="B54" s="3" t="s">
         <v>192</v>
       </c>
-      <c r="G54" s="0" t="s">
+      <c r="G54" s="3" t="s">
         <v>193</v>
       </c>
-      <c r="I54" s="0" t="s">
+      <c r="I54" s="3" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="0" t="s">
+      <c r="A55" s="3" t="s">
         <v>194</v>
       </c>
-      <c r="B55" s="0" t="s">
+      <c r="B55" s="3" t="s">
         <v>195</v>
       </c>
-      <c r="I55" s="0" t="s">
+      <c r="I55" s="3" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="0" t="s">
+      <c r="A56" s="3" t="s">
         <v>196</v>
       </c>
-      <c r="B56" s="0" t="s">
+      <c r="B56" s="3" t="s">
         <v>197</v>
       </c>
-      <c r="G56" s="0" t="s">
+      <c r="G56" s="3" t="s">
         <v>198</v>
       </c>
-      <c r="I56" s="0" t="s">
+      <c r="I56" s="3" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="0" t="s">
+      <c r="A57" s="3" t="s">
         <v>199</v>
       </c>
-      <c r="B57" s="0" t="s">
+      <c r="B57" s="3" t="s">
         <v>200</v>
       </c>
-      <c r="G57" s="0" t="s">
+      <c r="G57" s="3" t="s">
         <v>201</v>
       </c>
-      <c r="I57" s="0" t="s">
+      <c r="I57" s="3" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="0" t="s">
+      <c r="A58" s="3" t="s">
         <v>202</v>
       </c>
-      <c r="B58" s="0" t="s">
+      <c r="B58" s="3" t="s">
         <v>203</v>
       </c>
-      <c r="G58" s="0" t="s">
+      <c r="G58" s="3" t="s">
         <v>204</v>
       </c>
-      <c r="I58" s="0" t="s">
+      <c r="I58" s="3" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="0" t="s">
+      <c r="A59" s="3" t="s">
         <v>205</v>
       </c>
-      <c r="B59" s="0" t="s">
+      <c r="B59" s="3" t="s">
         <v>206</v>
       </c>
-      <c r="G59" s="0" t="s">
+      <c r="G59" s="3" t="s">
         <v>207</v>
       </c>
-      <c r="I59" s="0" t="s">
+      <c r="I59" s="3" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="0" t="s">
+      <c r="A60" s="3" t="s">
         <v>208</v>
       </c>
-      <c r="B60" s="0" t="s">
+      <c r="B60" s="3" t="s">
         <v>209</v>
       </c>
-      <c r="I60" s="0" t="s">
+      <c r="I60" s="3" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="0" t="s">
+      <c r="A61" s="3" t="s">
         <v>210</v>
       </c>
-      <c r="B61" s="0" t="s">
+      <c r="B61" s="3" t="s">
         <v>211</v>
       </c>
-      <c r="G61" s="0" t="s">
+      <c r="G61" s="3" t="s">
         <v>212</v>
       </c>
-      <c r="I61" s="0" t="s">
+      <c r="I61" s="3" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="0" t="s">
+      <c r="A62" s="3" t="s">
         <v>213</v>
       </c>
-      <c r="B62" s="0" t="s">
+      <c r="B62" s="3" t="s">
         <v>214</v>
       </c>
-      <c r="G62" s="0" t="s">
+      <c r="G62" s="3" t="s">
         <v>215</v>
       </c>
-      <c r="I62" s="0" t="s">
+      <c r="I62" s="3" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="0" t="s">
+      <c r="A63" s="3" t="s">
         <v>216</v>
       </c>
-      <c r="B63" s="0" t="s">
+      <c r="B63" s="3" t="s">
         <v>217</v>
       </c>
-      <c r="G63" s="0" t="s">
+      <c r="G63" s="3" t="s">
         <v>218</v>
       </c>
-      <c r="I63" s="0" t="s">
+      <c r="I63" s="3" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A64" s="0" t="s">
+      <c r="A64" s="3" t="s">
         <v>219</v>
       </c>
-      <c r="B64" s="0" t="s">
+      <c r="B64" s="3" t="s">
         <v>220</v>
       </c>
-      <c r="I64" s="0" t="s">
+      <c r="I64" s="3" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="0" t="s">
+      <c r="A65" s="3" t="s">
         <v>221</v>
       </c>
-      <c r="B65" s="0" t="s">
+      <c r="B65" s="3" t="s">
         <v>222</v>
       </c>
-      <c r="G65" s="0" t="s">
+      <c r="G65" s="3" t="s">
         <v>223</v>
       </c>
-      <c r="I65" s="0" t="s">
+      <c r="I65" s="3" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A66" s="0" t="s">
+      <c r="A66" s="3" t="s">
         <v>224</v>
       </c>
-      <c r="B66" s="0" t="s">
+      <c r="B66" s="3" t="s">
         <v>225</v>
       </c>
-      <c r="G66" s="0" t="s">
+      <c r="G66" s="3" t="s">
         <v>226</v>
       </c>
-      <c r="I66" s="0" t="s">
+      <c r="I66" s="3" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A67" s="0" t="s">
+      <c r="A67" s="3" t="s">
         <v>227</v>
       </c>
-      <c r="B67" s="0" t="s">
+      <c r="B67" s="3" t="s">
         <v>228</v>
       </c>
-      <c r="G67" s="0" t="s">
+      <c r="G67" s="3" t="s">
         <v>229</v>
       </c>
-      <c r="I67" s="0" t="s">
+      <c r="I67" s="3" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A68" s="0" t="s">
+      <c r="A68" s="3" t="s">
         <v>230</v>
       </c>
-      <c r="B68" s="0" t="s">
+      <c r="B68" s="3" t="s">
         <v>231</v>
       </c>
-      <c r="G68" s="0" t="s">
+      <c r="G68" s="3" t="s">
         <v>232</v>
       </c>
-      <c r="I68" s="0" t="s">
+      <c r="I68" s="3" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A69" s="0" t="s">
+      <c r="A69" s="3" t="s">
         <v>233</v>
       </c>
-      <c r="B69" s="0" t="s">
+      <c r="B69" s="3" t="s">
         <v>234</v>
       </c>
-      <c r="I69" s="0" t="s">
+      <c r="I69" s="3" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A70" s="0" t="s">
+      <c r="A70" s="3" t="s">
         <v>235</v>
       </c>
-      <c r="B70" s="0" t="s">
+      <c r="B70" s="3" t="s">
         <v>236</v>
       </c>
-      <c r="G70" s="0" t="s">
+      <c r="G70" s="3" t="s">
         <v>237</v>
       </c>
-      <c r="I70" s="0" t="s">
+      <c r="I70" s="3" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A71" s="0" t="s">
+      <c r="A71" s="3" t="s">
         <v>238</v>
       </c>
-      <c r="B71" s="0" t="s">
+      <c r="B71" s="3" t="s">
         <v>239</v>
       </c>
-      <c r="I71" s="0" t="s">
+      <c r="I71" s="3" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A72" s="0" t="s">
+      <c r="A72" s="3" t="s">
         <v>240</v>
       </c>
-      <c r="B72" s="0" t="s">
+      <c r="B72" s="3" t="s">
         <v>241</v>
       </c>
-      <c r="I72" s="0" t="s">
+      <c r="I72" s="3" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A73" s="0" t="s">
+      <c r="A73" s="3" t="s">
         <v>242</v>
       </c>
-      <c r="B73" s="0" t="s">
+      <c r="B73" s="3" t="s">
         <v>243</v>
       </c>
-      <c r="I73" s="0" t="s">
+      <c r="I73" s="3" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A74" s="0" t="s">
+      <c r="A74" s="3" t="s">
         <v>244</v>
       </c>
-      <c r="B74" s="0" t="s">
+      <c r="B74" s="3" t="s">
         <v>245</v>
       </c>
-      <c r="G74" s="0" t="s">
+      <c r="G74" s="3" t="s">
         <v>246</v>
       </c>
-      <c r="I74" s="0" t="s">
+      <c r="I74" s="3" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A75" s="0" t="s">
+      <c r="A75" s="3" t="s">
         <v>247</v>
       </c>
-      <c r="B75" s="0" t="s">
+      <c r="B75" s="3" t="s">
         <v>248</v>
       </c>
-      <c r="G75" s="0" t="s">
+      <c r="G75" s="3" t="s">
         <v>249</v>
       </c>
-      <c r="I75" s="0" t="s">
+      <c r="I75" s="3" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A76" s="0" t="s">
+      <c r="A76" s="3" t="s">
         <v>250</v>
       </c>
-      <c r="B76" s="0" t="s">
+      <c r="B76" s="3" t="s">
         <v>251</v>
       </c>
-      <c r="G76" s="0" t="s">
+      <c r="G76" s="3" t="s">
         <v>252</v>
       </c>
-      <c r="I76" s="0" t="s">
+      <c r="I76" s="3" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A77" s="0" t="s">
+      <c r="A77" s="3" t="s">
         <v>253</v>
       </c>
-      <c r="B77" s="0" t="s">
+      <c r="B77" s="3" t="s">
         <v>254</v>
       </c>
-      <c r="I77" s="0" t="s">
+      <c r="I77" s="3" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A78" s="0" t="s">
+      <c r="A78" s="3" t="s">
         <v>255</v>
       </c>
-      <c r="B78" s="0" t="s">
+      <c r="B78" s="3" t="s">
         <v>256</v>
       </c>
-      <c r="G78" s="0" t="s">
+      <c r="G78" s="3" t="s">
         <v>257</v>
       </c>
-      <c r="I78" s="0" t="s">
+      <c r="I78" s="3" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A79" s="0" t="s">
+      <c r="A79" s="3" t="s">
         <v>258</v>
       </c>
-      <c r="B79" s="0" t="s">
+      <c r="B79" s="3" t="s">
         <v>259</v>
       </c>
-      <c r="I79" s="0" t="s">
+      <c r="I79" s="3" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A80" s="0" t="s">
+      <c r="A80" s="3" t="s">
         <v>260</v>
       </c>
-      <c r="B80" s="0" t="s">
+      <c r="B80" s="3" t="s">
         <v>261</v>
       </c>
-      <c r="G80" s="0" t="s">
+      <c r="G80" s="3" t="s">
         <v>262</v>
       </c>
-      <c r="I80" s="0" t="s">
+      <c r="I80" s="3" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A81" s="0" t="s">
+      <c r="A81" s="3" t="s">
         <v>263</v>
       </c>
-      <c r="B81" s="0" t="s">
+      <c r="B81" s="3" t="s">
         <v>264</v>
       </c>
-      <c r="G81" s="0" t="s">
+      <c r="G81" s="3" t="s">
         <v>265</v>
       </c>
-      <c r="I81" s="0" t="s">
+      <c r="I81" s="3" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A82" s="0" t="s">
+      <c r="A82" s="3" t="s">
         <v>266</v>
       </c>
-      <c r="B82" s="0" t="s">
+      <c r="B82" s="3" t="s">
         <v>267</v>
       </c>
-      <c r="I82" s="0" t="s">
+      <c r="I82" s="3" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A83" s="0" t="s">
+      <c r="A83" s="3" t="s">
         <v>268</v>
       </c>
-      <c r="B83" s="0" t="s">
+      <c r="B83" s="3" t="s">
         <v>269</v>
       </c>
-      <c r="G83" s="0" t="s">
+      <c r="G83" s="3" t="s">
         <v>270</v>
       </c>
-      <c r="I83" s="0" t="s">
+      <c r="I83" s="3" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A84" s="0" t="s">
+      <c r="A84" s="3" t="s">
         <v>271</v>
       </c>
-      <c r="B84" s="0" t="s">
+      <c r="B84" s="3" t="s">
         <v>272</v>
       </c>
-      <c r="F84" s="0" t="s">
+      <c r="F84" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="G84" s="0" t="s">
+      <c r="G84" s="3" t="s">
         <v>273</v>
       </c>
-      <c r="I84" s="0" t="s">
+      <c r="I84" s="3" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A85" s="0" t="s">
+      <c r="A85" s="3" t="s">
         <v>274</v>
       </c>
-      <c r="B85" s="0" t="s">
+      <c r="B85" s="3" t="s">
         <v>275</v>
       </c>
-      <c r="I85" s="0" t="s">
+      <c r="I85" s="3" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A86" s="0" t="s">
+      <c r="A86" s="3" t="s">
         <v>276</v>
       </c>
-      <c r="B86" s="0" t="s">
+      <c r="B86" s="3" t="s">
         <v>277</v>
       </c>
-      <c r="F86" s="0" t="s">
+      <c r="F86" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="G86" s="0" t="s">
+      <c r="G86" s="3" t="s">
         <v>278</v>
       </c>
-      <c r="I86" s="0" t="s">
+      <c r="I86" s="3" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A87" s="0" t="s">
+      <c r="A87" s="3" t="s">
         <v>279</v>
       </c>
-      <c r="B87" s="0" t="s">
+      <c r="B87" s="3" t="s">
         <v>280</v>
       </c>
-      <c r="F87" s="0" t="s">
+      <c r="F87" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="G87" s="0" t="s">
+      <c r="G87" s="3" t="s">
         <v>281</v>
       </c>
-      <c r="I87" s="0" t="s">
+      <c r="I87" s="3" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A88" s="0" t="s">
+      <c r="A88" s="3" t="s">
         <v>282</v>
       </c>
-      <c r="B88" s="0" t="s">
+      <c r="B88" s="3" t="s">
         <v>283</v>
       </c>
-      <c r="F88" s="0" t="s">
+      <c r="F88" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="G88" s="0" t="s">
+      <c r="G88" s="3" t="s">
         <v>284</v>
       </c>
-      <c r="I88" s="0" t="s">
+      <c r="I88" s="3" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A89" s="0" t="s">
+      <c r="A89" s="3" t="s">
         <v>285</v>
       </c>
-      <c r="B89" s="0" t="s">
+      <c r="B89" s="3" t="s">
         <v>286</v>
       </c>
-      <c r="F89" s="0" t="s">
+      <c r="F89" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="G89" s="0" t="s">
+      <c r="G89" s="3" t="s">
         <v>287</v>
       </c>
-      <c r="I89" s="0" t="s">
+      <c r="I89" s="3" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A90" s="0" t="s">
+      <c r="A90" s="3" t="s">
         <v>288</v>
       </c>
-      <c r="B90" s="0" t="s">
+      <c r="B90" s="3" t="s">
         <v>289</v>
       </c>
-      <c r="F90" s="0" t="s">
+      <c r="F90" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="G90" s="0" t="s">
+      <c r="G90" s="3" t="s">
         <v>290</v>
       </c>
-      <c r="I90" s="0" t="s">
+      <c r="I90" s="3" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A91" s="0" t="s">
+      <c r="A91" s="3" t="s">
         <v>291</v>
       </c>
-      <c r="B91" s="0" t="s">
+      <c r="B91" s="3" t="s">
         <v>292</v>
       </c>
-      <c r="F91" s="0" t="s">
+      <c r="F91" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="G91" s="0" t="s">
+      <c r="G91" s="3" t="s">
         <v>293</v>
       </c>
-      <c r="I91" s="0" t="s">
+      <c r="I91" s="3" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A92" s="0" t="s">
+      <c r="A92" s="3" t="s">
         <v>294</v>
       </c>
-      <c r="B92" s="0" t="s">
+      <c r="B92" s="3" t="s">
         <v>295</v>
       </c>
-      <c r="G92" s="0" t="s">
-        <v>293</v>
-      </c>
-      <c r="I92" s="0" t="s">
+      <c r="G92" s="3" t="s">
+        <v>296</v>
+      </c>
+      <c r="I92" s="3" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A93" s="0" t="s">
-        <v>296</v>
-      </c>
-      <c r="I93" s="0" t="s">
+      <c r="A93" s="3" t="s">
+        <v>297</v>
+      </c>
+      <c r="I93" s="3" t="s">
         <v>14</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:I93"/>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -2799,5 +2853,6 @@
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/data/corpus_liste/bnr_corpus.xlsx
+++ b/data/corpus_liste/bnr_corpus.xlsx
@@ -376,7 +376,7 @@
     <t xml:space="preserve">RBX_AMR_DEL </t>
   </si>
   <si>
-    <t xml:space="preserve">AMR_DIA</t>
+    <t xml:space="preserve">AMR_9FI</t>
   </si>
   <si>
     <t xml:space="preserve">Archives - Diapositives</t>
@@ -541,7 +541,7 @@
     <t xml:space="preserve">Archives - Archives privées Roussel</t>
   </si>
   <si>
-    <t xml:space="preserve">AMR_VIC</t>
+    <t xml:space="preserve">AMR_5H</t>
   </si>
   <si>
     <t xml:space="preserve">Archives - Roubaisiens victimes des guerres</t>
@@ -1017,7 +1017,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
